--- a/Data/masterdoc.xlsx
+++ b/Data/masterdoc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/wos7466_ads_northwestern_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/715df1d5bf239437/Desktop/Critical_Mineral_Mines_Database/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3EA377B-9D47-4ADA-8D57-6D7B7472398C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{D3EA377B-9D47-4ADA-8D57-6D7B7472398C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF82B7D0-DC84-49DB-842D-8AF7BC07E4F0}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15920" xr2:uid="{2A3BBF91-037C-2B40-83C4-3B50E338CC8D}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{2A3BBF91-037C-2B40-83C4-3B50E338CC8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Chile" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,9 +38,9 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={80F92A82-3DBA-9242-A570-C81BFDF1FE53}</author>
-    <author>tc={12D92D52-3A7C-B24F-9152-A5639EB56B21}</author>
     <author>tc={0920DC59-6672-5E4C-8588-43402C8261C8}</author>
     <author>tc={DA0911C2-4E8A-8A4B-93B3-3BDB77995434}</author>
+    <author>tc={12D92D52-3A7C-B24F-9152-A5639EB56B21}</author>
     <author>tc={BF788312-42B2-6240-8F75-214C2B8CF30E}</author>
     <author>tc={722A52B9-66D9-AF46-9225-B7EAF1B1AD95}</author>
     <author>tc={65244721-D8F0-D047-9971-A281F098CA66}</author>
@@ -69,7 +67,25 @@
     Next data update can reference current production numbers - https://www.caserones.cl/nuestra-operacion/</t>
       </text>
     </comment>
-    <comment ref="G9" authorId="1" shapeId="0" xr:uid="{12D92D52-3A7C-B24F-9152-A5639EB56B21}">
+    <comment ref="A8" authorId="1" shapeId="0" xr:uid="{0920DC59-6672-5E4C-8588-43402C8261C8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Marking this as active although technically it’s a new construction “Nueva Centinela” that is
+Reply:
+    Also note this was formed by combining El Tesoro + Esperanza</t>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="2" shapeId="0" xr:uid="{DA0911C2-4E8A-8A4B-93B3-3BDB77995434}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    or 4929.2 (different tabs had different numbers)</t>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="3" shapeId="0" xr:uid="{12D92D52-3A7C-B24F-9152-A5639EB56B21}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -79,25 +95,7 @@
     I think it’s 1915 for the current true operation (1882 maybe minor, and not Codelco)</t>
       </text>
     </comment>
-    <comment ref="A11" authorId="2" shapeId="0" xr:uid="{0920DC59-6672-5E4C-8588-43402C8261C8}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Marking this as active although technically it’s a new construction “Nueva Centinela” that is
-Reply:
-    Also note this was formed by combining El Tesoro + Esperanza</t>
-      </text>
-    </comment>
-    <comment ref="M11" authorId="3" shapeId="0" xr:uid="{DA0911C2-4E8A-8A4B-93B3-3BDB77995434}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    or 4929.2 (different tabs had different numbers)</t>
-      </text>
-    </comment>
-    <comment ref="G15" authorId="4" shapeId="0" xr:uid="{BF788312-42B2-6240-8F75-214C2B8CF30E}">
+    <comment ref="G13" authorId="4" shapeId="0" xr:uid="{BF788312-42B2-6240-8F75-214C2B8CF30E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -105,7 +103,7 @@
     Updated from 1994 (probably someone got that from Wikipedia)</t>
       </text>
     </comment>
-    <comment ref="D21" authorId="5" shapeId="0" xr:uid="{722A52B9-66D9-AF46-9225-B7EAF1B1AD95}">
+    <comment ref="D18" authorId="5" shapeId="0" xr:uid="{722A52B9-66D9-AF46-9225-B7EAF1B1AD95}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -113,7 +111,7 @@
     I think it’s Coquimbo. Weird situation of this small mine being leased to another operator.</t>
       </text>
     </comment>
-    <comment ref="F21" authorId="6" shapeId="0" xr:uid="{65244721-D8F0-D047-9971-A281F098CA66}">
+    <comment ref="F18" authorId="6" shapeId="0" xr:uid="{65244721-D8F0-D047-9971-A281F098CA66}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -121,7 +119,7 @@
     Minera Los Vilos is the permanent owner and APG’s lease ended</t>
       </text>
     </comment>
-    <comment ref="A22" authorId="7" shapeId="0" xr:uid="{73842DBD-8749-664D-B503-8AB54A3C2FA6}">
+    <comment ref="A19" authorId="7" shapeId="0" xr:uid="{73842DBD-8749-664D-B503-8AB54A3C2FA6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -129,7 +127,7 @@
     Update to Rajo Inca, the new name. This one is technically inactive.</t>
       </text>
     </comment>
-    <comment ref="A26" authorId="8" shapeId="0" xr:uid="{7D5BA396-4D03-6148-AB3E-FF80A0861A1A}">
+    <comment ref="A23" authorId="8" shapeId="0" xr:uid="{7D5BA396-4D03-6148-AB3E-FF80A0861A1A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -137,7 +135,7 @@
     Inactive under this name, active under Centinela (was combined with Esperanza)</t>
       </text>
     </comment>
-    <comment ref="A27" authorId="9" shapeId="0" xr:uid="{53EB39D8-447D-614F-A1B0-BA5AE8B5A7DE}">
+    <comment ref="A24" authorId="9" shapeId="0" xr:uid="{53EB39D8-447D-614F-A1B0-BA5AE8B5A7DE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -145,7 +143,7 @@
     Inactive under this name, active under Centinela (was combined with El Tesoro)</t>
       </text>
     </comment>
-    <comment ref="A28" authorId="10" shapeId="0" xr:uid="{8838A87E-E5A1-7A40-BC99-BD9BB83796E8}">
+    <comment ref="A25" authorId="10" shapeId="0" xr:uid="{8838A87E-E5A1-7A40-BC99-BD9BB83796E8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -153,7 +151,7 @@
     Part of Centinela</t>
       </text>
     </comment>
-    <comment ref="G29" authorId="11" shapeId="0" xr:uid="{703E55ED-840E-DB40-B90D-C53F5E6D0734}">
+    <comment ref="G26" authorId="11" shapeId="0" xr:uid="{703E55ED-840E-DB40-B90D-C53F5E6D0734}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -161,7 +159,7 @@
     Not sure why this originally had 2028-2043, as it’s operational</t>
       </text>
     </comment>
-    <comment ref="A31" authorId="12" shapeId="0" xr:uid="{FD81F943-A2A9-EB4C-8D73-016E52EFF393}">
+    <comment ref="A28" authorId="12" shapeId="0" xr:uid="{FD81F943-A2A9-EB4C-8D73-016E52EFF393}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -169,7 +167,7 @@
     Distrito*</t>
       </text>
     </comment>
-    <comment ref="G36" authorId="13" shapeId="0" xr:uid="{2B7D7304-53CB-6B43-9C93-8A8C2BCDF967}">
+    <comment ref="G33" authorId="13" shapeId="0" xr:uid="{2B7D7304-53CB-6B43-9C93-8A8C2BCDF967}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -177,7 +175,7 @@
     Not sure why originally 1990. 25 year birthday was 2025.</t>
       </text>
     </comment>
-    <comment ref="H38" authorId="14" shapeId="0" xr:uid="{6EAB021A-CEBF-8D45-9D54-985411406C4A}">
+    <comment ref="H35" authorId="14" shapeId="0" xr:uid="{6EAB021A-CEBF-8D45-9D54-985411406C4A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -185,7 +183,7 @@
     Probably good to monitor status as they’re only getting low-grade ore at this point</t>
       </text>
     </comment>
-    <comment ref="A43" authorId="15" shapeId="0" xr:uid="{EE3E7D65-8C9D-B84D-AC0C-C2C4E0AFDCED}">
+    <comment ref="A41" authorId="15" shapeId="0" xr:uid="{EE3E7D65-8C9D-B84D-AC0C-C2C4E0AFDCED}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -193,7 +191,7 @@
     Update year to 2023 if Fase 2. Or take that out of name?</t>
       </text>
     </comment>
-    <comment ref="A45" authorId="16" shapeId="0" xr:uid="{AF8305BF-0DDE-A347-B8E7-C978A2E7C70B}">
+    <comment ref="A43" authorId="16" shapeId="0" xr:uid="{AF8305BF-0DDE-A347-B8E7-C978A2E7C70B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -201,7 +199,7 @@
     This is within Andina, not independent</t>
       </text>
     </comment>
-    <comment ref="M46" authorId="17" shapeId="0" xr:uid="{7CF704EB-E686-8A44-BB53-8AB2808F0D3E}">
+    <comment ref="M44" authorId="17" shapeId="0" xr:uid="{7CF704EB-E686-8A44-BB53-8AB2808F0D3E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -209,7 +207,7 @@
     175 Mm^3</t>
       </text>
     </comment>
-    <comment ref="A48" authorId="18" shapeId="0" xr:uid="{3905CC62-EED8-4047-B013-A7194FA0C828}">
+    <comment ref="A46" authorId="18" shapeId="0" xr:uid="{3905CC62-EED8-4047-B013-A7194FA0C828}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -217,7 +215,7 @@
     Salar Blanco is the name of the LPI project. Codelco et al. also trying to start operations in the future</t>
       </text>
     </comment>
-    <comment ref="F50" authorId="19" shapeId="0" xr:uid="{CF29182A-FFAB-1443-8755-6515CCC05494}">
+    <comment ref="F48" authorId="19" shapeId="0" xr:uid="{CF29182A-FFAB-1443-8755-6515CCC05494}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1814,7 +1812,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2113,7 +2111,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2165,6 +2162,7 @@
     <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2518,67 +2516,67 @@
   <threadedComment ref="A7" dT="2026-06-25T19:30:57.23" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{80F92A82-3DBA-9242-A570-C81BFDF1FE53}">
     <text>Next data update can reference current production numbers - https://www.caserones.cl/nuestra-operacion/</text>
   </threadedComment>
-  <threadedComment ref="G9" dT="2026-06-25T19:38:43.38" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{12D92D52-3A7C-B24F-9152-A5639EB56B21}">
+  <threadedComment ref="A8" dT="2026-06-25T19:51:31.01" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{0920DC59-6672-5E4C-8588-43402C8261C8}">
+    <text>Marking this as active although technically it’s a new construction “Nueva Centinela” that is</text>
+  </threadedComment>
+  <threadedComment ref="A8" dT="2026-06-25T20:59:49.27" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{F05D5DFD-245C-214F-A654-04112012EB0C}" parentId="{0920DC59-6672-5E4C-8588-43402C8261C8}">
+    <text>Also note this was formed by combining El Tesoro + Esperanza</text>
+  </threadedComment>
+  <threadedComment ref="M8" dT="2026-06-23T21:15:13.79" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{DA0911C2-4E8A-8A4B-93B3-3BDB77995434}">
+    <text>or 4929.2 (different tabs had different numbers)</text>
+  </threadedComment>
+  <threadedComment ref="G10" dT="2026-06-25T19:38:43.38" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{12D92D52-3A7C-B24F-9152-A5639EB56B21}">
     <text>1915? https://consejominero.cl/nosotros/mapa-minero/chuquicamata/</text>
   </threadedComment>
-  <threadedComment ref="G9" dT="2026-06-25T19:41:57.63" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{E98598D8-5FC6-4740-9A53-22D991A0781B}" parentId="{12D92D52-3A7C-B24F-9152-A5639EB56B21}">
+  <threadedComment ref="G10" dT="2026-06-25T19:41:57.63" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{E98598D8-5FC6-4740-9A53-22D991A0781B}" parentId="{12D92D52-3A7C-B24F-9152-A5639EB56B21}">
     <text>I think it’s 1915 for the current true operation (1882 maybe minor, and not Codelco)</text>
   </threadedComment>
-  <threadedComment ref="A11" dT="2026-06-25T19:51:31.01" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{0920DC59-6672-5E4C-8588-43402C8261C8}">
-    <text>Marking this as active although technically it’s a new construction “Nueva Centinela” that is</text>
-  </threadedComment>
-  <threadedComment ref="A11" dT="2026-06-25T20:59:49.27" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{F05D5DFD-245C-214F-A654-04112012EB0C}" parentId="{0920DC59-6672-5E4C-8588-43402C8261C8}">
-    <text>Also note this was formed by combining El Tesoro + Esperanza</text>
-  </threadedComment>
-  <threadedComment ref="M11" dT="2026-06-23T21:15:13.79" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{DA0911C2-4E8A-8A4B-93B3-3BDB77995434}">
-    <text>or 4929.2 (different tabs had different numbers)</text>
-  </threadedComment>
-  <threadedComment ref="G15" dT="2026-06-25T20:07:03.38" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{BF788312-42B2-6240-8F75-214C2B8CF30E}">
+  <threadedComment ref="G13" dT="2026-06-25T20:07:03.38" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{BF788312-42B2-6240-8F75-214C2B8CF30E}">
     <text>Updated from 1994 (probably someone got that from Wikipedia)</text>
   </threadedComment>
-  <threadedComment ref="D21" dT="2026-06-25T20:27:36.44" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{722A52B9-66D9-AF46-9225-B7EAF1B1AD95}">
+  <threadedComment ref="D18" dT="2026-06-25T20:27:36.44" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{722A52B9-66D9-AF46-9225-B7EAF1B1AD95}">
     <text>I think it’s Coquimbo. Weird situation of this small mine being leased to another operator.</text>
   </threadedComment>
-  <threadedComment ref="F21" dT="2026-06-25T20:29:51.64" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{65244721-D8F0-D047-9971-A281F098CA66}">
+  <threadedComment ref="F18" dT="2026-06-25T20:29:51.64" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{65244721-D8F0-D047-9971-A281F098CA66}">
     <text>Minera Los Vilos is the permanent owner and APG’s lease ended</text>
   </threadedComment>
-  <threadedComment ref="A22" dT="2026-06-25T20:35:31.84" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{73842DBD-8749-664D-B503-8AB54A3C2FA6}">
+  <threadedComment ref="A19" dT="2026-06-25T20:35:31.84" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{73842DBD-8749-664D-B503-8AB54A3C2FA6}">
     <text>Update to Rajo Inca, the new name. This one is technically inactive.</text>
   </threadedComment>
-  <threadedComment ref="A26" dT="2026-06-25T21:04:26.20" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{7D5BA396-4D03-6148-AB3E-FF80A0861A1A}">
+  <threadedComment ref="A23" dT="2026-06-25T21:04:26.20" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{7D5BA396-4D03-6148-AB3E-FF80A0861A1A}">
     <text>Inactive under this name, active under Centinela (was combined with Esperanza)</text>
   </threadedComment>
-  <threadedComment ref="A27" dT="2026-06-25T21:05:06.32" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{53EB39D8-447D-614F-A1B0-BA5AE8B5A7DE}">
+  <threadedComment ref="A24" dT="2026-06-25T21:05:06.32" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{53EB39D8-447D-614F-A1B0-BA5AE8B5A7DE}">
     <text>Inactive under this name, active under Centinela (was combined with El Tesoro)</text>
   </threadedComment>
-  <threadedComment ref="A28" dT="2026-06-25T21:11:25.90" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{8838A87E-E5A1-7A40-BC99-BD9BB83796E8}">
+  <threadedComment ref="A25" dT="2026-06-25T21:11:25.90" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{8838A87E-E5A1-7A40-BC99-BD9BB83796E8}">
     <text>Part of Centinela</text>
   </threadedComment>
-  <threadedComment ref="G29" dT="2026-06-25T21:13:39.48" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{703E55ED-840E-DB40-B90D-C53F5E6D0734}">
+  <threadedComment ref="G26" dT="2026-06-25T21:13:39.48" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{703E55ED-840E-DB40-B90D-C53F5E6D0734}">
     <text>Not sure why this originally had 2028-2043, as it’s operational</text>
   </threadedComment>
-  <threadedComment ref="A31" dT="2026-06-25T21:17:57.33" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{FD81F943-A2A9-EB4C-8D73-016E52EFF393}">
+  <threadedComment ref="A28" dT="2026-06-25T21:17:57.33" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{FD81F943-A2A9-EB4C-8D73-016E52EFF393}">
     <text>Distrito*</text>
   </threadedComment>
-  <threadedComment ref="G36" dT="2026-06-25T21:28:38.90" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{2B7D7304-53CB-6B43-9C93-8A8C2BCDF967}">
+  <threadedComment ref="G33" dT="2026-06-25T21:28:38.90" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{2B7D7304-53CB-6B43-9C93-8A8C2BCDF967}">
     <text>Not sure why originally 1990. 25 year birthday was 2025.</text>
   </threadedComment>
-  <threadedComment ref="H38" dT="2026-06-25T21:33:21.09" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{6EAB021A-CEBF-8D45-9D54-985411406C4A}">
+  <threadedComment ref="H35" dT="2026-06-25T21:33:21.09" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{6EAB021A-CEBF-8D45-9D54-985411406C4A}">
     <text>Probably good to monitor status as they’re only getting low-grade ore at this point</text>
   </threadedComment>
-  <threadedComment ref="A43" dT="2026-06-25T21:57:02.31" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{EE3E7D65-8C9D-B84D-AC0C-C2C4E0AFDCED}">
+  <threadedComment ref="A41" dT="2026-06-25T21:57:02.31" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{EE3E7D65-8C9D-B84D-AC0C-C2C4E0AFDCED}">
     <text>Update year to 2023 if Fase 2. Or take that out of name?</text>
   </threadedComment>
-  <threadedComment ref="A45" dT="2026-06-25T22:00:11.03" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{AF8305BF-0DDE-A347-B8E7-C978A2E7C70B}">
+  <threadedComment ref="A43" dT="2026-06-25T22:00:11.03" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{AF8305BF-0DDE-A347-B8E7-C978A2E7C70B}">
     <text>This is within Andina, not independent</text>
   </threadedComment>
-  <threadedComment ref="M46" dT="2026-06-26T22:21:31.00" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{7CF704EB-E686-8A44-BB53-8AB2808F0D3E}">
+  <threadedComment ref="M44" dT="2026-06-26T22:21:31.00" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{7CF704EB-E686-8A44-BB53-8AB2808F0D3E}">
     <text>175 Mm^3</text>
   </threadedComment>
-  <threadedComment ref="A48" dT="2026-06-25T22:06:15.53" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{3905CC62-EED8-4047-B013-A7194FA0C828}">
+  <threadedComment ref="A46" dT="2026-06-25T22:06:15.53" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{3905CC62-EED8-4047-B013-A7194FA0C828}">
     <text>Salar Blanco is the name of the LPI project. Codelco et al. also trying to start operations in the future</text>
   </threadedComment>
-  <threadedComment ref="F50" dT="2026-06-25T22:13:41.91" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{CF29182A-FFAB-1443-8755-6515CCC05494}">
+  <threadedComment ref="F48" dT="2026-06-25T22:13:41.91" personId="{2C84671C-7BB1-F143-9CBF-68D1A1FD2BFD}" id="{CF29182A-FFAB-1443-8755-6515CCC05494}">
     <text>Previously said “Salar Blanco Mining Company?” but it was sold</text>
   </threadedComment>
 </ThreadedComments>
@@ -2613,15 +2611,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183C1B38-8EA9-6140-B0D0-E82B3A873638}">
   <dimension ref="A1:X53"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="32.5" customWidth="1"/>
-    <col min="14" max="14" width="21.375" customWidth="1"/>
+    <col min="14" max="14" width="21.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="23" customFormat="1" ht="131.1" thickBot="1">
+    <row r="1" spans="1:24" s="23" customFormat="1" ht="129" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2679,7 +2677,7 @@
       <c r="W1" s="22"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" ht="17.100000000000001" thickTop="1">
+    <row r="2" spans="1:24" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>16</v>
       </c>
@@ -2725,7 +2723,7 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>24</v>
       </c>
@@ -2769,7 +2767,7 @@
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>30</v>
       </c>
@@ -2815,7 +2813,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>34</v>
       </c>
@@ -2865,7 +2863,7 @@
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
@@ -2914,7 +2912,7 @@
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>47</v>
       </c>
@@ -2964,90 +2962,92 @@
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
     </row>
-    <row r="8" spans="1:24">
-      <c r="A8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="10">
-        <v>-20.044443999999999</v>
-      </c>
-      <c r="C8" s="10">
-        <v>-69.264722000000006</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>54</v>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="11">
+        <v>-22.975155999999998</v>
+      </c>
+      <c r="C8" s="11">
+        <v>-69.061419000000001</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>57</v>
+      <c r="F8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="11">
+        <v>2014</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="12">
-        <v>35</v>
-      </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+        <v>223.8</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="12">
+        <v>2.4</v>
+      </c>
       <c r="M8" s="12">
-        <v>1610</v>
+        <v>5185.3999999999996</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B9" s="10">
-        <v>-22.299721999999999</v>
+        <v>-20.044443999999999</v>
       </c>
       <c r="C9" s="10">
-        <v>-68.895278000000005</v>
+        <v>-69.264722000000006</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="10">
-        <v>1882</v>
+        <v>55</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J9" s="12">
-        <v>248.5</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>50</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="12"/>
       <c r="M9" s="12">
-        <v>14571</v>
+        <v>1610</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O9" s="5"/>
       <c r="R9" s="1"/>
@@ -3055,42 +3055,46 @@
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="10">
-        <v>-30.713000000000001</v>
+        <v>-22.299721999999999</v>
       </c>
       <c r="C10" s="10">
-        <v>-71.213999999999999</v>
+        <v>-68.895278000000005</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="25"/>
+        <v>26</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1882</v>
+      </c>
       <c r="H10" s="10" t="s">
         <v>20</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="12"/>
+      <c r="J10" s="12">
+        <v>248.5</v>
+      </c>
       <c r="K10" s="12" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="12">
-        <v>3.35</v>
+        <v>14571</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>64</v>
@@ -3099,27 +3103,27 @@
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B11" s="11">
-        <v>-22.975155999999998</v>
+        <v>-20.968056000000001</v>
       </c>
       <c r="C11" s="11">
-        <v>-69.061419000000001</v>
+        <v>-68.685556000000005</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G11" s="11">
-        <v>2014</v>
+        <v>1999</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>20</v>
@@ -3128,19 +3132,17 @@
         <v>21</v>
       </c>
       <c r="J11" s="12">
-        <v>223.8</v>
+        <v>560</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="L11" s="12">
-        <v>2.4</v>
-      </c>
+      <c r="L11" s="12"/>
       <c r="M11" s="12">
-        <v>5185.3999999999996</v>
+        <v>9975</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
@@ -3152,27 +3154,27 @@
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B12" s="11">
-        <v>-20.968056000000001</v>
+        <v>-32.563333</v>
       </c>
       <c r="C12" s="11">
-        <v>-68.685556000000005</v>
+        <v>-70.853333000000006</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="11">
-        <v>1999</v>
+        <v>77</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>20</v>
@@ -3180,18 +3182,14 @@
       <c r="I12" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J12" s="12">
-        <v>560</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>50</v>
-      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
       <c r="L12" s="12"/>
       <c r="M12" s="12">
-        <v>9975</v>
+        <v>21.1</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
@@ -3203,42 +3201,44 @@
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B13" s="11">
-        <v>-32.676000000000002</v>
+        <v>-22.683</v>
       </c>
       <c r="C13" s="11">
-        <v>-70.896000000000001</v>
+        <v>-70.177999999999997</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="11"/>
+        <v>81</v>
+      </c>
+      <c r="G13" s="11">
+        <v>1959</v>
+      </c>
       <c r="H13" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12" t="s">
-        <v>22</v>
-      </c>
+      <c r="J13" s="12">
+        <v>21</v>
+      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="12"/>
       <c r="M13" s="12">
-        <v>2.5</v>
+        <v>16</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1" t="s">
@@ -3247,69 +3247,71 @@
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B14" s="11">
-        <v>-32.563333</v>
+        <v>-24.968</v>
       </c>
       <c r="C14" s="11">
-        <v>-70.853333000000006</v>
+        <v>-70.393000000000001</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>20</v>
+        <v>85</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>57</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
+      <c r="K14" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="L14" s="12"/>
       <c r="M14" s="12">
-        <v>21.1</v>
+        <v>15</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B15" s="11">
-        <v>-22.683</v>
+        <v>-30.460999999999999</v>
       </c>
       <c r="C15" s="11">
-        <v>-70.177999999999997</v>
+        <v>-71.218999999999994</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="11">
-        <v>1959</v>
+        <v>89</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>90</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>20</v>
@@ -3317,16 +3319,14 @@
       <c r="I15" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J15" s="12">
-        <v>21</v>
-      </c>
+      <c r="J15" s="12"/>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
       <c r="M15" s="12">
-        <v>16</v>
+        <v>9.1389999999999993</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1" t="s">
@@ -3335,71 +3335,69 @@
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B16" s="11">
-        <v>-24.968</v>
+        <v>-28.991</v>
       </c>
       <c r="C16" s="11">
-        <v>-70.393000000000001</v>
+        <v>-70.88</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16" s="26" t="s">
-        <v>57</v>
+        <v>73</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="12" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="L16" s="12"/>
       <c r="M16" s="12">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B17" s="11">
-        <v>-30.460999999999999</v>
+        <v>-21.924167000000001</v>
       </c>
       <c r="C17" s="11">
-        <v>-71.218999999999994</v>
+        <v>-68.834166999999994</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>90</v>
+        <v>102</v>
+      </c>
+      <c r="G17" s="11">
+        <v>1996</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>20</v>
@@ -3407,14 +3405,18 @@
       <c r="I17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
+      <c r="J17" s="12">
+        <v>98.4</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12">
-        <v>9.1389999999999993</v>
+        <v>2991</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1" t="s">
@@ -3423,109 +3425,115 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B18" s="11">
-        <v>-29.888999999999999</v>
+        <v>-32.029000000000003</v>
       </c>
       <c r="C18" s="11">
-        <v>-70.882000000000005</v>
+        <v>-71.188000000000002</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="11"/>
+      <c r="F18" s="11" t="s">
+        <v>106</v>
+      </c>
       <c r="G18" s="11"/>
-      <c r="H18" s="26" t="s">
-        <v>94</v>
+      <c r="H18" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B19" s="11">
-        <v>-28.991</v>
+        <v>-26.241389000000002</v>
       </c>
       <c r="C19" s="11">
-        <v>-70.88</v>
+        <v>-69.569999999999993</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>109</v>
+      </c>
       <c r="H19" s="11" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="12"/>
+      <c r="J19" s="12">
+        <v>13</v>
+      </c>
       <c r="K19" s="12" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12">
-        <v>36</v>
+        <v>3569</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B20" s="11">
-        <v>-21.924167000000001</v>
+        <v>-32.457000000000001</v>
       </c>
       <c r="C20" s="11">
-        <v>-68.834166999999994</v>
+        <v>-71.070999999999998</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="G20" s="11">
-        <v>1996</v>
+        <v>-2033</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>20</v>
@@ -3533,18 +3541,14 @@
       <c r="I20" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="12">
-        <v>98.4</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>50</v>
-      </c>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
       <c r="L20" s="12"/>
       <c r="M20" s="12">
-        <v>2991</v>
+        <v>1.83</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="O20" s="6"/>
       <c r="R20" s="1"/>
@@ -3552,60 +3556,60 @@
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B21" s="11">
-        <v>-32.029000000000003</v>
+        <v>-32.611666999999997</v>
       </c>
       <c r="C21" s="11">
-        <v>-71.188000000000002</v>
+        <v>-71.127499999999998</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21" s="11"/>
+        <v>114</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>115</v>
+      </c>
       <c r="H21" s="11" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="I21" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J21" s="12"/>
-      <c r="K21" s="12" t="s">
-        <v>98</v>
-      </c>
+      <c r="K21" s="12"/>
       <c r="L21" s="12"/>
       <c r="M21" s="12">
-        <v>0.5</v>
+        <v>237</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B22" s="11">
-        <v>-26.241389000000002</v>
+        <v>-34.091667000000001</v>
       </c>
       <c r="C22" s="11">
-        <v>-69.569999999999993</v>
+        <v>-70.338333000000006</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>18</v>
@@ -3613,27 +3617,27 @@
       <c r="F22" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>109</v>
+      <c r="G22" s="11">
+        <v>1905</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J22" s="12">
-        <v>13</v>
+        <v>351.9</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12">
-        <v>3569</v>
+        <v>16613</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="O22" s="5"/>
       <c r="R22" s="1"/>
@@ -3641,29 +3645,29 @@
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B23" s="11">
-        <v>-32.457000000000001</v>
+        <v>-22.953099999999999</v>
       </c>
       <c r="C23" s="11">
-        <v>-71.070999999999998</v>
+        <v>-69.073099999999997</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="11">
-        <v>-2033</v>
-      </c>
-      <c r="H23" s="11" t="s">
+      <c r="F23" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" s="27" t="s">
         <v>20</v>
       </c>
       <c r="I23" s="12" t="s">
@@ -3673,52 +3677,58 @@
       <c r="K23" s="12"/>
       <c r="L23" s="12"/>
       <c r="M23" s="12">
-        <v>1.83</v>
+        <v>127</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B24" s="11">
-        <v>-32.611666999999997</v>
+        <v>-22.975000000000001</v>
       </c>
       <c r="C24" s="11">
-        <v>-71.127499999999998</v>
+        <v>-69.063000000000002</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>114</v>
+      <c r="F24" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="H24" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" s="27" t="s">
         <v>20</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
+      <c r="J24" s="12">
+        <v>190</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" s="12">
+        <v>2</v>
+      </c>
       <c r="M24" s="12">
-        <v>237</v>
+        <v>1287</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>117</v>
@@ -3727,46 +3737,44 @@
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B25" s="11">
-        <v>-34.091667000000001</v>
+        <v>-22.972999999999999</v>
       </c>
       <c r="C25" s="11">
-        <v>-70.338333000000006</v>
+        <v>-69.091999999999999</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>26</v>
+      <c r="F25" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="G25" s="11">
-        <v>1905</v>
-      </c>
-      <c r="H25" s="11" t="s">
+        <v>2023</v>
+      </c>
+      <c r="H25" s="27" t="s">
         <v>20</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="12">
-        <v>351.9</v>
-      </c>
+      <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12">
-        <v>16613</v>
+        <v>1995</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="O25" s="5"/>
       <c r="R25" s="1"/>
@@ -3774,15 +3782,15 @@
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B26" s="11">
-        <v>-22.953099999999999</v>
+        <v>-25.829000000000001</v>
       </c>
       <c r="C26" s="11">
-        <v>-69.073099999999997</v>
+        <v>-69.864000000000004</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>17</v>
@@ -3790,121 +3798,119 @@
       <c r="E26" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="32" t="s">
-        <v>122</v>
+      <c r="F26" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="H26" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="H26" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
+      <c r="K26" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12">
-        <v>127</v>
+        <v>27</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
     </row>
-    <row r="27" spans="1:21">
-      <c r="A27" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="B27" s="11">
-        <v>-22.975000000000001</v>
-      </c>
-      <c r="C27" s="11">
-        <v>-69.063000000000002</v>
-      </c>
-      <c r="D27" s="11" t="s">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="10">
+        <v>-23.418299999999999</v>
+      </c>
+      <c r="C27" s="10">
+        <v>-68.811099999999996</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="H27" s="27" t="s">
+      <c r="F27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>20</v>
       </c>
       <c r="I27" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J27" s="12">
-        <v>190</v>
+        <v>105.8</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="L27" s="12">
-        <v>2</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="L27" s="12"/>
       <c r="M27" s="12">
-        <v>1287</v>
+        <v>2239</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="O27" s="5"/>
-      <c r="R27" s="31" t="s">
+      <c r="R27" s="30" t="s">
         <v>128</v>
       </c>
       <c r="S27" s="1"/>
       <c r="T27" s="2"/>
       <c r="U27" s="1"/>
     </row>
-    <row r="28" spans="1:21">
-      <c r="A28" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="B28" s="11">
-        <v>-22.972999999999999</v>
-      </c>
-      <c r="C28" s="11">
-        <v>-69.091999999999999</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>17</v>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="10">
+        <v>-26.838000000000001</v>
+      </c>
+      <c r="C28" s="10">
+        <v>-69.953999999999994</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28" s="11">
-        <v>2023</v>
-      </c>
-      <c r="H28" s="27" t="s">
-        <v>20</v>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10">
+        <v>1869</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="I28" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12">
-        <v>1995</v>
+        <v>769</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="O28" s="5"/>
       <c r="P28" s="7"/>
@@ -3914,44 +3920,46 @@
       <c r="T28" s="2"/>
       <c r="U28" s="1"/>
     </row>
-    <row r="29" spans="1:21">
-      <c r="A29" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="B29" s="11">
-        <v>-25.829000000000001</v>
-      </c>
-      <c r="C29" s="11">
-        <v>-69.864000000000004</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>17</v>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="10">
+        <v>-24.274999999999999</v>
+      </c>
+      <c r="C29" s="10">
+        <v>-69.058333000000005</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="H29" s="11" t="s">
+      <c r="F29" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>20</v>
       </c>
       <c r="I29" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="12"/>
+      <c r="J29" s="12">
+        <v>1125</v>
+      </c>
       <c r="K29" s="12" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12">
-        <v>27</v>
+        <v>19400</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="1" t="s">
@@ -3960,15 +3968,15 @@
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B30" s="10">
-        <v>-23.418299999999999</v>
+        <v>-25.698</v>
       </c>
       <c r="C30" s="10">
-        <v>-68.811099999999996</v>
+        <v>-70.495999999999995</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>17</v>
@@ -3977,10 +3985,10 @@
         <v>18</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>20</v>
@@ -3988,18 +3996,16 @@
       <c r="I30" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J30" s="12">
-        <v>105.8</v>
-      </c>
+      <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12">
-        <v>2239</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="O30" s="5"/>
       <c r="R30" s="1"/>
@@ -4007,42 +4013,44 @@
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B31" s="10">
-        <v>-26.838000000000001</v>
+        <v>-23.431388999999999</v>
       </c>
       <c r="C31" s="10">
-        <v>-69.953999999999994</v>
+        <v>-69.506666999999993</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10">
-        <v>1869</v>
+      <c r="F31" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>152</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="I31" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J31" s="12"/>
       <c r="K31" s="12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="12">
-        <v>769</v>
+        <v>2410</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="O31" s="5"/>
       <c r="R31" s="1"/>
@@ -4050,27 +4058,27 @@
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B32" s="10">
-        <v>-24.274999999999999</v>
+        <v>-33.151000000000003</v>
       </c>
       <c r="C32" s="10">
-        <v>-69.058333000000005</v>
+        <v>-70.284999999999997</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>142</v>
+        <v>156</v>
+      </c>
+      <c r="G32" s="10">
+        <v>1867</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>20</v>
@@ -4078,18 +4086,16 @@
       <c r="I32" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J32" s="12">
-        <v>1125</v>
-      </c>
+      <c r="J32" s="12"/>
       <c r="K32" s="12" t="s">
         <v>50</v>
       </c>
       <c r="L32" s="12"/>
       <c r="M32" s="12">
-        <v>19400</v>
+        <v>6384</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="O32" s="5"/>
       <c r="R32" s="1" t="s">
@@ -4101,27 +4107,27 @@
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B33" s="10">
-        <v>-25.698</v>
+        <v>-31.715</v>
       </c>
       <c r="C33" s="10">
-        <v>-70.495999999999995</v>
+        <v>-70.499443999999997</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>147</v>
+        <v>160</v>
+      </c>
+      <c r="G33" s="10">
+        <v>2000</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>20</v>
@@ -4131,14 +4137,16 @@
       </c>
       <c r="J33" s="12"/>
       <c r="K33" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L33" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="L33" s="12">
+        <v>8.3000000000000007</v>
+      </c>
       <c r="M33" s="12">
-        <v>2.2999999999999998</v>
+        <v>5957.4</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1" t="s">
@@ -4147,27 +4155,27 @@
       <c r="T33" s="1"/>
       <c r="U33" s="1"/>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B34" s="10">
-        <v>-23.431388999999999</v>
+        <v>-26.558889000000001</v>
       </c>
       <c r="C34" s="10">
-        <v>-69.506666999999993</v>
+        <v>-70.314999999999998</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>152</v>
+        <v>164</v>
+      </c>
+      <c r="G34" s="10">
+        <v>1995</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>20</v>
@@ -4177,14 +4185,14 @@
       </c>
       <c r="J34" s="12"/>
       <c r="K34" s="12" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L34" s="12"/>
       <c r="M34" s="12">
-        <v>2410</v>
+        <v>482.7</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="O34" s="5"/>
       <c r="R34" s="1" t="s">
@@ -4194,27 +4202,27 @@
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B35" s="10">
-        <v>-33.151000000000003</v>
+        <v>-23.421666999999999</v>
       </c>
       <c r="C35" s="10">
-        <v>-70.284999999999997</v>
+        <v>-70.071667000000005</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="G35" s="10">
-        <v>1867</v>
+        <v>168</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>20</v>
@@ -4222,16 +4230,18 @@
       <c r="I35" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J35" s="12"/>
+      <c r="J35" s="12">
+        <v>50</v>
+      </c>
       <c r="K35" s="12" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="L35" s="12"/>
       <c r="M35" s="12">
-        <v>6384</v>
+        <v>329</v>
       </c>
       <c r="N35" s="13" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="O35" s="5"/>
       <c r="R35" s="1" t="s">
@@ -4241,46 +4251,40 @@
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B36" s="10">
-        <v>-31.715</v>
+        <v>-22.382999999999999</v>
       </c>
       <c r="C36" s="10">
-        <v>-70.499443999999997</v>
+        <v>-70.218000000000004</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="G36" s="10">
-        <v>2000</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="G36" s="10"/>
       <c r="H36" s="10" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J36" s="12"/>
-      <c r="K36" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="L36" s="12">
-        <v>8.3000000000000007</v>
-      </c>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
       <c r="M36" s="12">
-        <v>5957.4</v>
+        <v>22.5</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
@@ -4292,44 +4296,42 @@
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B37" s="10">
-        <v>-26.558889000000001</v>
+        <v>-22.530999999999999</v>
       </c>
       <c r="C37" s="10">
-        <v>-70.314999999999998</v>
+        <v>-70.221000000000004</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G37" s="10">
-        <v>1995</v>
+        <v>176</v>
+      </c>
+      <c r="G37" s="28" t="s">
+        <v>177</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="I37" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="12"/>
-      <c r="K37" s="12" t="s">
-        <v>38</v>
-      </c>
+      <c r="K37" s="12"/>
       <c r="L37" s="12"/>
       <c r="M37" s="12">
-        <v>482.7</v>
+        <v>4.5</v>
       </c>
       <c r="N37" s="13" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>165</v>
@@ -4340,46 +4342,44 @@
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B38" s="10">
-        <v>-23.421666999999999</v>
+        <v>-34.008000000000003</v>
       </c>
       <c r="C38" s="10">
-        <v>-70.071667000000005</v>
+        <v>-70.977999999999994</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>20</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J38" s="12">
-        <v>50</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="J38" s="12"/>
       <c r="K38" s="12" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="L38" s="12"/>
       <c r="M38" s="12">
-        <v>329</v>
+        <v>11.4</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>171</v>
@@ -4390,15 +4390,15 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B39" s="10">
-        <v>-22.382999999999999</v>
+        <v>-22.378799999999998</v>
       </c>
       <c r="C39" s="10">
-        <v>-70.218000000000004</v>
+        <v>-68.913300000000007</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>17</v>
@@ -4407,109 +4407,119 @@
         <v>18</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="G39" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="G39" s="28">
+        <v>2010</v>
+      </c>
       <c r="H39" s="10" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="I39" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
+      <c r="J39" s="12">
+        <v>126</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="L39" s="12"/>
       <c r="M39" s="12">
-        <v>22.5</v>
+        <v>3044</v>
       </c>
       <c r="N39" s="13" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="B40" s="10">
-        <v>-22.530999999999999</v>
+        <v>-30.713000000000001</v>
       </c>
       <c r="C40" s="10">
-        <v>-70.221000000000004</v>
+        <v>-71.213999999999999</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="G40" s="28" t="s">
-        <v>177</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="G40" s="25"/>
       <c r="H40" s="10" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="I40" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
+      <c r="K40" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="L40" s="12"/>
       <c r="M40" s="12">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B41" s="10">
-        <v>-34.008000000000003</v>
+        <v>-21.007000000000001</v>
       </c>
       <c r="C41" s="10">
-        <v>-70.977999999999994</v>
+        <v>-68.811999999999998</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>182</v>
+        <v>190</v>
+      </c>
+      <c r="G41" s="10">
+        <v>1971</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>20</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="J41" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="J41" s="12">
+        <v>208</v>
+      </c>
       <c r="K41" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="L41" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>191</v>
+      </c>
       <c r="M41" s="12">
-        <v>11.4</v>
+        <v>1594.2</v>
       </c>
       <c r="N41" s="13" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="R41" t="s">
         <v>186</v>
@@ -4518,15 +4528,15 @@
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B42" s="10">
-        <v>-22.378799999999998</v>
+        <v>-22.226944</v>
       </c>
       <c r="C42" s="10">
-        <v>-68.913300000000007</v>
+        <v>-68.883332999999993</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>17</v>
@@ -4537,8 +4547,8 @@
       <c r="F42" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G42" s="28">
-        <v>2010</v>
+      <c r="G42" s="10">
+        <v>1995</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>20</v>
@@ -4547,17 +4557,15 @@
         <v>21</v>
       </c>
       <c r="J42" s="12">
-        <v>126</v>
-      </c>
-      <c r="K42" s="12" t="s">
-        <v>50</v>
-      </c>
+        <v>314.8</v>
+      </c>
+      <c r="K42" s="12"/>
       <c r="L42" s="12"/>
       <c r="M42" s="12">
-        <v>3044</v>
+        <v>7394</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="O42" s="5"/>
       <c r="R42" s="1"/>
@@ -4565,48 +4573,44 @@
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B43" s="10">
-        <v>-21.007000000000001</v>
+        <v>-33.149000000000001</v>
       </c>
       <c r="C43" s="10">
-        <v>-68.811999999999998</v>
+        <v>-70.254000000000005</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="G43" s="10">
-        <v>1971</v>
-      </c>
-      <c r="H43" s="10" t="s">
+        <v>1970</v>
+      </c>
+      <c r="H43" s="27" t="s">
         <v>20</v>
       </c>
       <c r="I43" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J43" s="12">
-        <v>208</v>
-      </c>
+      <c r="J43" s="12"/>
       <c r="K43" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="L43" s="12" t="s">
-        <v>191</v>
-      </c>
+      <c r="L43" s="12"/>
       <c r="M43" s="12">
-        <v>1594.2</v>
+        <v>21969</v>
       </c>
       <c r="N43" s="13" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="O43" s="5"/>
       <c r="R43" s="1"/>
@@ -4616,89 +4620,85 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
     </row>
-    <row r="44" spans="1:21">
-      <c r="A44" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="B44" s="10">
-        <v>-22.226944</v>
-      </c>
-      <c r="C44" s="10">
-        <v>-68.883332999999993</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>17</v>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B44" s="11">
+        <v>-23.552</v>
+      </c>
+      <c r="C44" s="11">
+        <v>-68.378</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>200</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="10">
-        <v>1995</v>
-      </c>
-      <c r="H44" s="10" t="s">
+      <c r="F44" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="H44" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="12" t="s">
-        <v>21</v>
+      <c r="I44" s="15" t="s">
+        <v>203</v>
       </c>
       <c r="J44" s="12">
-        <v>314.8</v>
+        <v>13</v>
       </c>
       <c r="K44" s="12"/>
       <c r="L44" s="12"/>
-      <c r="M44" s="12">
-        <v>7394</v>
+      <c r="M44" s="28">
+        <v>0.26250000000000001</v>
       </c>
       <c r="N44" s="13" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
     </row>
-    <row r="45" spans="1:21">
-      <c r="A45" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B45" s="10">
-        <v>-33.149000000000001</v>
-      </c>
-      <c r="C45" s="10">
-        <v>-70.254000000000005</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>25</v>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A45" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B45" s="11">
+        <v>-23.552</v>
+      </c>
+      <c r="C45" s="11">
+        <v>-68.378</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>200</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10">
-        <v>1970</v>
-      </c>
-      <c r="H45" s="27" t="s">
+      <c r="F45" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="G45" s="11">
+        <v>1993</v>
+      </c>
+      <c r="H45" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="I45" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12" t="s">
-        <v>50</v>
-      </c>
+      <c r="I45" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="J45" s="12">
+        <v>53.5</v>
+      </c>
+      <c r="K45" s="12"/>
       <c r="L45" s="12"/>
-      <c r="M45" s="12">
-        <v>21969</v>
-      </c>
-      <c r="N45" s="13" t="s">
-        <v>197</v>
-      </c>
+      <c r="M45" s="12"/>
+      <c r="N45" s="13"/>
       <c r="O45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" t="s">
@@ -4707,44 +4707,38 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="B46" s="11">
-        <v>-23.552</v>
+        <v>-26.882000000000001</v>
       </c>
       <c r="C46" s="11">
-        <v>-68.378</v>
+        <v>-69.063000000000002</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>202</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G46" s="11"/>
       <c r="H46" s="11" t="s">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="J46" s="12">
-        <v>13</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="J46" s="12"/>
       <c r="K46" s="12"/>
       <c r="L46" s="12"/>
-      <c r="M46" s="28">
-        <v>0.26250000000000001</v>
-      </c>
+      <c r="M46" s="12"/>
       <c r="N46" s="13" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="O46" s="5"/>
       <c r="R46" s="1" t="s">
@@ -4758,41 +4752,41 @@
       </c>
       <c r="U46" s="1"/>
     </row>
-    <row r="47" spans="1:21">
-      <c r="A47" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="B47" s="11">
-        <v>-23.552</v>
-      </c>
-      <c r="C47" s="11">
-        <v>-68.378</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>200</v>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A47" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B47" s="10">
+        <v>-20.402000000000001</v>
+      </c>
+      <c r="C47" s="10">
+        <v>-70.123000000000005</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="G47" s="11">
-        <v>1993</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="J47" s="12">
-        <v>53.5</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" s="12"/>
       <c r="K47" s="12"/>
       <c r="L47" s="12"/>
-      <c r="M47" s="12"/>
-      <c r="N47" s="13"/>
+      <c r="M47" s="12">
+        <v>5.2</v>
+      </c>
+      <c r="N47" s="13" t="s">
+        <v>219</v>
+      </c>
       <c r="O47" s="5"/>
       <c r="R47" s="1"/>
       <c r="S47" t="s">
@@ -4801,38 +4795,44 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
     </row>
-    <row r="48" spans="1:21">
-      <c r="A48" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="B48" s="11">
-        <v>-26.882000000000001</v>
-      </c>
-      <c r="C48" s="11">
-        <v>-69.063000000000002</v>
-      </c>
-      <c r="D48" s="11" t="s">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B48" s="10">
+        <v>-23.239000000000001</v>
+      </c>
+      <c r="C48" s="10">
+        <v>-70.119</v>
+      </c>
+      <c r="D48" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F48" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>214</v>
+      <c r="F48" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G48" s="10">
+        <v>2022</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
+      <c r="K48" s="12" t="s">
+        <v>222</v>
+      </c>
       <c r="L48" s="12"/>
-      <c r="M48" s="12"/>
+      <c r="M48" s="12">
+        <v>92</v>
+      </c>
       <c r="N48" s="13" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="O48" s="5"/>
       <c r="R48" s="1"/>
@@ -4842,67 +4842,75 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B49" s="10">
-        <v>-20.402000000000001</v>
+        <v>-22.847200000000001</v>
       </c>
       <c r="C49" s="10">
-        <v>-70.123000000000005</v>
+        <v>-69.338899999999995</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F49" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="G49" s="10"/>
+      <c r="F49" s="54" t="s">
+        <v>225</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>226</v>
+      </c>
       <c r="H49" s="10" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="I49" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
-      <c r="L49" s="12"/>
+      <c r="J49" s="12">
+        <v>150.19999999999999</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L49" s="12">
+        <v>3</v>
+      </c>
       <c r="M49" s="12">
-        <v>5.2</v>
+        <v>2917</v>
       </c>
       <c r="N49" s="13" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B50" s="10">
-        <v>-23.239000000000001</v>
+        <v>-22.689167000000001</v>
       </c>
       <c r="C50" s="10">
-        <v>-70.119</v>
+        <v>-69.181388999999996</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="G50" s="10">
-        <v>2022</v>
+        <v>55</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>20</v>
@@ -4910,64 +4918,58 @@
       <c r="I50" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J50" s="12"/>
+      <c r="J50" s="12">
+        <v>244</v>
+      </c>
       <c r="K50" s="12" t="s">
-        <v>222</v>
+        <v>50</v>
       </c>
       <c r="L50" s="12"/>
       <c r="M50" s="12">
-        <v>92</v>
+        <v>2390</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
     </row>
-    <row r="51" spans="1:21">
-      <c r="A51" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="B51" s="10">
-        <v>-22.847200000000001</v>
-      </c>
-      <c r="C51" s="10">
-        <v>-69.338899999999995</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>17</v>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A51" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="11">
+        <v>-29.888999999999999</v>
+      </c>
+      <c r="C51" s="11">
+        <v>-70.882000000000005</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>20</v>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="26" t="s">
+        <v>94</v>
       </c>
       <c r="I51" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J51" s="12">
-        <v>150.19999999999999</v>
-      </c>
+      <c r="J51" s="12"/>
       <c r="K51" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="L51" s="12">
-        <v>3</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="L51" s="12"/>
       <c r="M51" s="12">
-        <v>2917</v>
+        <v>15</v>
       </c>
       <c r="N51" s="13" t="s">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c r="O51" s="5"/>
       <c r="R51" s="1" t="s">
@@ -4979,56 +4981,52 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
     </row>
-    <row r="52" spans="1:21">
-      <c r="A52" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B52" s="10">
-        <v>-22.689167000000001</v>
-      </c>
-      <c r="C52" s="10">
-        <v>-69.181388999999996</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>17</v>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A52" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" s="11">
+        <v>-32.676000000000002</v>
+      </c>
+      <c r="C52" s="11">
+        <v>-70.896000000000001</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F52" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="H52" s="10" t="s">
+      <c r="F52" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I52" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J52" s="12">
-        <v>244</v>
-      </c>
+      <c r="J52" s="12"/>
       <c r="K52" s="12" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="L52" s="12"/>
       <c r="M52" s="12">
-        <v>2390</v>
+        <v>2.5</v>
       </c>
       <c r="N52" s="13" t="s">
-        <v>232</v>
+        <v>74</v>
       </c>
       <c r="O52" s="5"/>
-      <c r="R52" s="30" t="s">
+      <c r="R52" s="29" t="s">
         <v>233</v>
       </c>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
         <v>234</v>
       </c>
@@ -5080,2491 +5078,2494 @@
       <c r="U53" s="1"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N53">
+    <sortCondition ref="A1:A53"/>
+  </sortState>
   <hyperlinks>
     <hyperlink ref="T46" r:id="rId1" xr:uid="{C1B02B38-2AF7-7748-81FB-825FB44A1C88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14993455-40FC-6640-BD39-FAB49A6BF1F6}">
   <dimension ref="A1:Y51"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.59765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="23" customFormat="1" ht="131.1" thickBot="1">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:25" s="23" customFormat="1" ht="129" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="I1" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="N1" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="36" t="s">
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="36" t="s">
+      <c r="S1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="37"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="39"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="38"/>
       <c r="W1" s="22"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:25" ht="17.100000000000001" thickTop="1">
-      <c r="A2" s="46" t="s">
+    <row r="2" spans="1:25" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="45" t="s">
         <v>238</v>
       </c>
-      <c r="B2" s="47">
+      <c r="B2" s="46">
         <v>-11.8348</v>
       </c>
-      <c r="C2" s="47">
+      <c r="C2" s="46">
         <v>142.04490000000001</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="G2" s="47" t="s">
         <v>242</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="J2" s="50">
+      <c r="J2" s="49">
         <v>5</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="K2" s="49" t="s">
         <v>244</v>
       </c>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50">
+      <c r="L2" s="49"/>
+      <c r="M2" s="49">
         <v>114.4</v>
       </c>
-      <c r="N2" s="50" t="s">
+      <c r="N2" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33" t="s">
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="46" t="s">
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" s="45" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="47">
+      <c r="B3" s="46">
         <v>-12.261100000000001</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="46">
         <v>136.83699999999999</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F3" s="48" t="s">
+      <c r="F3" s="47" t="s">
         <v>250</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="47" t="s">
         <v>251</v>
       </c>
-      <c r="H3" s="48" t="s">
+      <c r="H3" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="49" t="s">
+      <c r="I3" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="J3" s="50">
+      <c r="J3" s="49">
         <v>11800</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" s="49" t="s">
         <v>244</v>
       </c>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50">
+      <c r="L3" s="49"/>
+      <c r="M3" s="49">
         <v>10</v>
       </c>
-      <c r="N3" s="50" t="s">
+      <c r="N3" s="49" t="s">
         <v>252</v>
       </c>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33" t="s">
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="S3" s="33" t="s">
+      <c r="S3" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="33"/>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="46" t="s">
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" s="45" t="s">
         <v>255</v>
       </c>
-      <c r="B4" s="47">
+      <c r="B4" s="46">
         <v>-32.555799999999998</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="46">
         <v>116.1665</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="H4" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="49" t="s">
+      <c r="I4" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="J4" s="50">
+      <c r="J4" s="49">
         <v>23800</v>
       </c>
-      <c r="K4" s="50" t="s">
+      <c r="K4" s="49" t="s">
         <v>244</v>
       </c>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33" t="s">
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="46" t="s">
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" s="45" t="s">
         <v>260</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="46">
         <v>-12.6637</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="46">
         <v>141.8732</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="E5" s="48" t="s">
+      <c r="E5" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F5" s="48" t="s">
+      <c r="F5" s="47" t="s">
         <v>250</v>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="47">
         <v>1963</v>
       </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="49" t="s">
+      <c r="H5" s="47"/>
+      <c r="I5" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="49">
         <v>37000</v>
       </c>
-      <c r="K5" s="50" t="s">
+      <c r="K5" s="49" t="s">
         <v>244</v>
       </c>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50">
+      <c r="L5" s="49"/>
+      <c r="M5" s="49">
         <v>545</v>
       </c>
-      <c r="N5" s="50" t="s">
+      <c r="N5" s="49" t="s">
         <v>261</v>
       </c>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33" t="s">
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="S5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-    </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="46" t="s">
+      <c r="S5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" s="45" t="s">
         <v>263</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="46">
         <v>-32.845100000000002</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="46">
         <v>116.06180000000001</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="49" t="s">
+      <c r="I6" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="J6" s="50">
+      <c r="J6" s="49">
         <v>10000</v>
       </c>
-      <c r="K6" s="50" t="s">
+      <c r="K6" s="49" t="s">
         <v>266</v>
       </c>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33" t="s">
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="A7" s="46" t="s">
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="46">
         <v>-32.929200000000002</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="46">
         <v>116.4559</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="49" t="s">
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50" t="s">
+      <c r="J7" s="49"/>
+      <c r="K7" s="49" t="s">
         <v>244</v>
       </c>
-      <c r="L7" s="50">
+      <c r="L7" s="49">
         <v>3.8</v>
       </c>
-      <c r="M7" s="50">
+      <c r="M7" s="49">
         <v>1090</v>
       </c>
-      <c r="N7" s="50" t="s">
+      <c r="N7" s="49" t="s">
         <v>270</v>
       </c>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33" t="s">
+      <c r="O7" s="32"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="32" t="s">
         <v>271</v>
       </c>
-      <c r="S7" s="33" t="s">
+      <c r="S7" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
-    </row>
-    <row r="8" spans="1:25">
-      <c r="A8" s="46" t="s">
+      <c r="X7" s="32"/>
+      <c r="Y7" s="32"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" s="45" t="s">
         <v>273</v>
       </c>
-      <c r="B8" s="48">
+      <c r="B8" s="47">
         <v>-23.49194</v>
       </c>
-      <c r="C8" s="48">
+      <c r="C8" s="47">
         <v>120.27556</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="47" t="s">
         <v>274</v>
       </c>
-      <c r="G8" s="48" t="s">
+      <c r="G8" s="47" t="s">
         <v>275</v>
       </c>
-      <c r="H8" s="48" t="s">
+      <c r="H8" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="51" t="s">
+      <c r="I8" s="50" t="s">
         <v>276</v>
       </c>
-      <c r="J8" s="50">
+      <c r="J8" s="49">
         <v>452</v>
       </c>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50">
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49">
         <v>1.5</v>
       </c>
-      <c r="N8" s="50" t="s">
+      <c r="N8" s="49" t="s">
         <v>277</v>
       </c>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33" t="s">
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32" t="s">
         <v>278</v>
       </c>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-    </row>
-    <row r="9" spans="1:25">
-      <c r="A9" s="46" t="s">
+      <c r="X8" s="32"/>
+      <c r="Y8" s="32"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" s="45" t="s">
         <v>279</v>
       </c>
-      <c r="B9" s="48">
+      <c r="B9" s="47">
         <v>-33.456350710000002</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="47">
         <v>148.99649450000001</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="47" t="s">
         <v>281</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="47" t="s">
         <v>282</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="H9" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="49" t="s">
+      <c r="I9" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="50">
+      <c r="J9" s="49">
         <v>85</v>
       </c>
-      <c r="K9" s="50" t="s">
+      <c r="K9" s="49" t="s">
         <v>283</v>
       </c>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50">
+      <c r="L9" s="49"/>
+      <c r="M9" s="49">
         <v>2.1</v>
       </c>
-      <c r="N9" s="50" t="s">
+      <c r="N9" s="49" t="s">
         <v>284</v>
       </c>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33" t="s">
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="S9" s="33" t="s">
+      <c r="S9" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
-    </row>
-    <row r="10" spans="1:25">
-      <c r="A10" s="46" t="s">
+      <c r="X9" s="32"/>
+      <c r="Y9" s="32"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" s="45" t="s">
         <v>287</v>
       </c>
-      <c r="B10" s="48">
+      <c r="B10" s="47">
         <v>-31.24172476</v>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="47">
         <v>137.48186770000001</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="F10" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="G10" s="48" t="s">
+      <c r="G10" s="47" t="s">
         <v>290</v>
       </c>
-      <c r="H10" s="48" t="s">
+      <c r="H10" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="49" t="s">
+      <c r="I10" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="50">
+      <c r="J10" s="49">
         <v>4250</v>
       </c>
-      <c r="K10" s="50" t="s">
+      <c r="K10" s="49" t="s">
         <v>291</v>
       </c>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50">
+      <c r="L10" s="49"/>
+      <c r="M10" s="49">
         <v>900</v>
       </c>
-      <c r="N10" s="50" t="s">
+      <c r="N10" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33" t="s">
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="S10" s="33" t="s">
+      <c r="S10" s="32" t="s">
         <v>293</v>
       </c>
-      <c r="T10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-      <c r="Y10" s="33"/>
-    </row>
-    <row r="11" spans="1:25">
-      <c r="A11" s="46" t="s">
+      <c r="T10" s="32"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="32"/>
+      <c r="Y10" s="32"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A11" s="45" t="s">
         <v>294</v>
       </c>
-      <c r="B11" s="48">
+      <c r="B11" s="47">
         <v>-31.408000000000001</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="47">
         <v>145.80099999999999</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" s="47" t="s">
         <v>295</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="47" t="s">
         <v>296</v>
       </c>
-      <c r="H11" s="48" t="s">
+      <c r="H11" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="49" t="s">
+      <c r="I11" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="50" t="s">
+      <c r="J11" s="49" t="s">
         <v>297</v>
       </c>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50">
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49">
         <v>8</v>
       </c>
-      <c r="N11" s="50" t="s">
+      <c r="N11" s="49" t="s">
         <v>298</v>
       </c>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33" t="s">
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="S11" s="33" t="s">
+      <c r="S11" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="V11" s="34"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33"/>
-      <c r="Y11" s="33"/>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="A12" s="46" t="s">
+      <c r="V11" s="33"/>
+      <c r="W11" s="32"/>
+      <c r="X11" s="32"/>
+      <c r="Y11" s="32"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A12" s="45" t="s">
         <v>301</v>
       </c>
-      <c r="B12" s="48">
+      <c r="B12" s="47">
         <v>-20.953056</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="47">
         <v>140.978611</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="F12" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="47">
         <v>1996</v>
       </c>
-      <c r="H12" s="48"/>
-      <c r="I12" s="49" t="s">
+      <c r="H12" s="47"/>
+      <c r="I12" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J12" s="50">
+      <c r="J12" s="49">
         <v>10.6</v>
       </c>
-      <c r="K12" s="50" t="s">
+      <c r="K12" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50">
+      <c r="L12" s="49"/>
+      <c r="M12" s="49">
         <v>6.2</v>
       </c>
-      <c r="N12" s="50" t="s">
+      <c r="N12" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33" t="s">
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32" t="s">
         <v>305</v>
       </c>
-      <c r="S12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="33"/>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="A13" s="46" t="s">
+      <c r="S12" s="32"/>
+      <c r="W12" s="32"/>
+      <c r="X12" s="32"/>
+      <c r="Y12" s="32"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A13" s="45" t="s">
         <v>306</v>
       </c>
-      <c r="B13" s="48">
+      <c r="B13" s="47">
         <v>-20.444305549999999</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="47">
         <v>140.71826239999999</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="E13" s="48" t="s">
+      <c r="E13" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F13" s="48" t="s">
+      <c r="F13" s="47" t="s">
         <v>307</v>
       </c>
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="47" t="s">
         <v>308</v>
       </c>
-      <c r="H13" s="48" t="s">
+      <c r="H13" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="49" t="s">
+      <c r="I13" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="50">
+      <c r="J13" s="49">
         <v>52</v>
       </c>
-      <c r="K13" s="50" t="s">
+      <c r="K13" s="49" t="s">
         <v>291</v>
       </c>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50">
+      <c r="L13" s="49"/>
+      <c r="M13" s="49">
         <v>97</v>
       </c>
-      <c r="N13" s="50" t="s">
+      <c r="N13" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33" t="s">
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="A14" s="46" t="s">
+      <c r="W13" s="32"/>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="32"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" s="45" t="s">
         <v>310</v>
       </c>
-      <c r="B14" s="48">
+      <c r="B14" s="47">
         <v>-28.7450698</v>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="47">
         <v>116.946304</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="47" t="s">
         <v>311</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F14" s="48" t="s">
+      <c r="F14" s="47" t="s">
         <v>312</v>
       </c>
-      <c r="G14" s="48" t="s">
+      <c r="G14" s="47" t="s">
         <v>313</v>
       </c>
-      <c r="H14" s="48"/>
-      <c r="I14" s="49" t="s">
+      <c r="H14" s="47"/>
+      <c r="I14" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="50">
+      <c r="J14" s="49">
         <v>18.100000000000001</v>
       </c>
-      <c r="K14" s="50" t="s">
+      <c r="K14" s="49" t="s">
         <v>314</v>
       </c>
-      <c r="L14" s="50">
+      <c r="L14" s="49">
         <v>51.5</v>
       </c>
-      <c r="M14" s="50">
+      <c r="M14" s="49">
         <v>53.8</v>
       </c>
-      <c r="N14" s="50" t="s">
+      <c r="N14" s="49" t="s">
         <v>315</v>
       </c>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33" t="s">
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32" t="s">
         <v>316</v>
       </c>
-      <c r="S14" s="33" t="s">
+      <c r="S14" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="33"/>
-    </row>
-    <row r="15" spans="1:25">
-      <c r="A15" s="46" t="s">
+      <c r="W14" s="32"/>
+      <c r="X14" s="32"/>
+      <c r="Y14" s="32"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A15" s="45" t="s">
         <v>318</v>
       </c>
-      <c r="B15" s="48">
+      <c r="B15" s="47">
         <v>-35.095762790000002</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="47">
         <v>138.99625209999999</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="E15" s="48" t="s">
+      <c r="E15" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="47" t="s">
         <v>319</v>
       </c>
-      <c r="G15" s="48" t="s">
+      <c r="G15" s="47" t="s">
         <v>320</v>
       </c>
-      <c r="H15" s="48" t="s">
+      <c r="H15" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="49" t="s">
+      <c r="I15" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J15" s="52" t="s">
+      <c r="J15" s="51" t="s">
         <v>321</v>
       </c>
-      <c r="K15" s="50" t="s">
+      <c r="K15" s="49" t="s">
         <v>291</v>
       </c>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50">
+      <c r="L15" s="49"/>
+      <c r="M15" s="49">
         <v>19.3</v>
       </c>
-      <c r="N15" s="50" t="s">
+      <c r="N15" s="49" t="s">
         <v>322</v>
       </c>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33" t="s">
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32" t="s">
         <v>323</v>
       </c>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-    </row>
-    <row r="16" spans="1:25">
-      <c r="A16" s="46" t="s">
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
+      <c r="Y15" s="32"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A16" s="45" t="s">
         <v>324</v>
       </c>
-      <c r="B16" s="48">
+      <c r="B16" s="47">
         <v>-20.722327530000001</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="47">
         <v>139.4772983</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="E16" s="48" t="s">
+      <c r="E16" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F16" s="48" t="s">
+      <c r="F16" s="47" t="s">
         <v>325</v>
       </c>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="47" t="s">
         <v>326</v>
       </c>
-      <c r="H16" s="48" t="s">
+      <c r="H16" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="49" t="s">
+      <c r="I16" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J16" s="50">
+      <c r="J16" s="49">
         <v>6100</v>
       </c>
-      <c r="K16" s="50" t="s">
+      <c r="K16" s="49" t="s">
         <v>327</v>
       </c>
-      <c r="L16" s="50">
+      <c r="L16" s="49">
         <v>4600</v>
       </c>
-      <c r="M16" s="50">
+      <c r="M16" s="49">
         <v>521</v>
       </c>
-      <c r="N16" s="50" t="s">
+      <c r="N16" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33" t="s">
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="S16" s="33" t="s">
+      <c r="S16" s="32" t="s">
         <v>330</v>
       </c>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="33"/>
-    </row>
-    <row r="17" spans="1:25">
-      <c r="A17" s="46" t="s">
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A17" s="45" t="s">
         <v>331</v>
       </c>
-      <c r="B17" s="48">
+      <c r="B17" s="47">
         <v>-32.936800939999998</v>
       </c>
-      <c r="C17" s="48">
+      <c r="C17" s="47">
         <v>148.06362150000001</v>
       </c>
-      <c r="D17" s="48" t="s">
+      <c r="D17" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="E17" s="48" t="s">
+      <c r="E17" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F17" s="48" t="s">
+      <c r="F17" s="47" t="s">
         <v>332</v>
       </c>
-      <c r="G17" s="48" t="s">
+      <c r="G17" s="47" t="s">
         <v>333</v>
       </c>
-      <c r="H17" s="48" t="s">
+      <c r="H17" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="49" t="s">
+      <c r="I17" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="50" t="s">
+      <c r="J17" s="49" t="s">
         <v>334</v>
       </c>
-      <c r="K17" s="50" t="s">
+      <c r="K17" s="49" t="s">
         <v>291</v>
       </c>
-      <c r="L17" s="50"/>
-      <c r="M17" s="50">
+      <c r="L17" s="49"/>
+      <c r="M17" s="49">
         <v>420.8</v>
       </c>
-      <c r="N17" s="50" t="s">
+      <c r="N17" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33" t="s">
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="32" t="s">
         <v>335</v>
       </c>
-      <c r="Y17" s="33"/>
-    </row>
-    <row r="18" spans="1:25">
-      <c r="A18" s="46" t="s">
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A18" s="45" t="s">
         <v>336</v>
       </c>
-      <c r="B18" s="48">
+      <c r="B18" s="47">
         <v>-31.809779509999998</v>
       </c>
-      <c r="C18" s="48">
+      <c r="C18" s="47">
         <v>123.17348819999999</v>
       </c>
-      <c r="D18" s="48" t="s">
+      <c r="D18" s="47" t="s">
         <v>311</v>
       </c>
-      <c r="E18" s="48" t="s">
+      <c r="E18" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F18" s="48" t="s">
+      <c r="F18" s="47" t="s">
         <v>337</v>
       </c>
-      <c r="G18" s="48">
+      <c r="G18" s="47">
         <v>2017</v>
       </c>
-      <c r="H18" s="48" t="s">
+      <c r="H18" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="49" t="s">
+      <c r="I18" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="50">
+      <c r="J18" s="49">
         <v>10.199999999999999</v>
       </c>
-      <c r="K18" s="50" t="s">
+      <c r="K18" s="49" t="s">
         <v>338</v>
       </c>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50">
+      <c r="L18" s="49"/>
+      <c r="M18" s="49">
         <v>14.3</v>
       </c>
-      <c r="N18" s="50" t="s">
+      <c r="N18" s="49" t="s">
         <v>339</v>
       </c>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33" t="s">
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="32" t="s">
         <v>340</v>
       </c>
-      <c r="W18" s="33"/>
-      <c r="X18" s="33"/>
-      <c r="Y18" s="33"/>
-    </row>
-    <row r="19" spans="1:25">
-      <c r="A19" s="46" t="s">
+      <c r="W18" s="32"/>
+      <c r="X18" s="32"/>
+      <c r="Y18" s="32"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A19" s="45" t="s">
         <v>341</v>
       </c>
-      <c r="B19" s="48">
+      <c r="B19" s="47">
         <v>-30.440590239999999</v>
       </c>
-      <c r="C19" s="48">
+      <c r="C19" s="47">
         <v>136.8717805</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="E19" s="48" t="s">
+      <c r="E19" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F19" s="48" t="s">
+      <c r="F19" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="G19" s="48" t="s">
+      <c r="G19" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="H19" s="48" t="s">
+      <c r="H19" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="49" t="s">
+      <c r="I19" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="50">
+      <c r="J19" s="49">
         <v>220</v>
       </c>
-      <c r="K19" s="50" t="s">
+      <c r="K19" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50">
+      <c r="L19" s="49"/>
+      <c r="M19" s="49">
         <v>11370</v>
       </c>
-      <c r="N19" s="50" t="s">
+      <c r="N19" s="49" t="s">
         <v>344</v>
       </c>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33" t="s">
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32" t="s">
         <v>345</v>
       </c>
-      <c r="W19" s="33"/>
-      <c r="X19" s="33"/>
-      <c r="Y19" s="33"/>
-    </row>
-    <row r="20" spans="1:25">
-      <c r="A20" s="46" t="s">
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A20" s="45" t="s">
         <v>346</v>
       </c>
-      <c r="B20" s="48">
+      <c r="B20" s="47">
         <v>-29.727807420000001</v>
       </c>
-      <c r="C20" s="48">
+      <c r="C20" s="47">
         <v>135.56475570000001</v>
       </c>
-      <c r="D20" s="48" t="s">
+      <c r="D20" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="E20" s="48" t="s">
+      <c r="E20" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F20" s="48" t="s">
+      <c r="F20" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="G20" s="48" t="s">
+      <c r="G20" s="47" t="s">
         <v>347</v>
       </c>
-      <c r="H20" s="48" t="s">
+      <c r="H20" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="49" t="s">
+      <c r="I20" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="50">
+      <c r="J20" s="49">
         <v>60.1</v>
       </c>
-      <c r="K20" s="50" t="s">
+      <c r="K20" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50">
+      <c r="L20" s="49"/>
+      <c r="M20" s="49">
         <v>158</v>
       </c>
-      <c r="N20" s="50" t="s">
+      <c r="N20" s="49" t="s">
         <v>348</v>
       </c>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33" t="s">
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32" t="s">
         <v>349</v>
       </c>
-      <c r="W20" s="33"/>
-      <c r="X20" s="33"/>
-      <c r="Y20" s="33"/>
-    </row>
-    <row r="21" spans="1:25">
-      <c r="A21" s="46" t="s">
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A21" s="45" t="s">
         <v>350</v>
       </c>
-      <c r="B21" s="48">
+      <c r="B21" s="47">
         <v>-21.729378629999999</v>
       </c>
-      <c r="C21" s="48">
+      <c r="C21" s="47">
         <v>122.21382680000001</v>
       </c>
-      <c r="D21" s="48" t="s">
+      <c r="D21" s="47" t="s">
         <v>311</v>
       </c>
-      <c r="E21" s="48" t="s">
+      <c r="E21" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F21" s="48" t="s">
+      <c r="F21" s="47" t="s">
         <v>351</v>
       </c>
-      <c r="G21" s="48" t="s">
+      <c r="G21" s="47" t="s">
         <v>352</v>
       </c>
-      <c r="H21" s="48"/>
-      <c r="I21" s="49" t="s">
+      <c r="H21" s="47"/>
+      <c r="I21" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="52" t="s">
+      <c r="J21" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="K21" s="50" t="s">
+      <c r="K21" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50">
+      <c r="L21" s="49"/>
+      <c r="M21" s="49">
         <v>154</v>
       </c>
-      <c r="N21" s="50" t="s">
+      <c r="N21" s="49" t="s">
         <v>354</v>
       </c>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33" t="s">
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32" t="s">
         <v>355</v>
       </c>
-      <c r="Y21" s="33"/>
-    </row>
-    <row r="22" spans="1:25">
-      <c r="A22" s="46" t="s">
+      <c r="Y21" s="32"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A22" s="45" t="s">
         <v>356</v>
       </c>
-      <c r="B22" s="48">
+      <c r="B22" s="47">
         <v>-31.510445910000001</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="46">
         <v>122.18373099999999</v>
       </c>
-      <c r="D22" s="48" t="s">
+      <c r="D22" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="E22" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F22" s="48" t="s">
+      <c r="F22" s="47" t="s">
         <v>357</v>
       </c>
-      <c r="G22" s="48" t="s">
+      <c r="G22" s="47" t="s">
         <v>358</v>
       </c>
-      <c r="H22" s="47" t="s">
+      <c r="H22" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="I22" s="51" t="s">
+      <c r="I22" s="50" t="s">
         <v>359</v>
       </c>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50" t="s">
+      <c r="J22" s="49"/>
+      <c r="K22" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50">
+      <c r="L22" s="49"/>
+      <c r="M22" s="49">
         <v>58.1</v>
       </c>
-      <c r="N22" s="50" t="s">
+      <c r="N22" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33" t="s">
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32" t="s">
         <v>362</v>
       </c>
-      <c r="X22" s="33"/>
-      <c r="Y22" s="33"/>
-    </row>
-    <row r="23" spans="1:25">
-      <c r="A23" s="46" t="s">
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A23" s="45" t="s">
         <v>363</v>
       </c>
-      <c r="B23" s="48">
+      <c r="B23" s="47">
         <v>-33.851397380000002</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="46">
         <v>116.059144</v>
       </c>
-      <c r="D23" s="48" t="s">
+      <c r="D23" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E23" s="48" t="s">
+      <c r="E23" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F23" s="48" t="s">
+      <c r="F23" s="47" t="s">
         <v>364</v>
       </c>
-      <c r="G23" s="48" t="s">
+      <c r="G23" s="47" t="s">
         <v>365</v>
       </c>
-      <c r="H23" s="47"/>
-      <c r="I23" s="51" t="s">
+      <c r="H23" s="46"/>
+      <c r="I23" s="50" t="s">
         <v>359</v>
       </c>
-      <c r="J23" s="50">
+      <c r="J23" s="49">
         <v>1950</v>
       </c>
-      <c r="K23" s="50" t="s">
+      <c r="K23" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50">
+      <c r="L23" s="49"/>
+      <c r="M23" s="49">
         <v>447</v>
       </c>
-      <c r="N23" s="50" t="s">
+      <c r="N23" s="49" t="s">
         <v>366</v>
       </c>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="33" t="s">
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="S23" s="33" t="s">
+      <c r="S23" s="32" t="s">
         <v>368</v>
       </c>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="33"/>
-      <c r="Y23" s="33"/>
-    </row>
-    <row r="24" spans="1:25">
-      <c r="A24" s="46" t="s">
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A24" s="45" t="s">
         <v>369</v>
       </c>
-      <c r="B24" s="48">
+      <c r="B24" s="47">
         <v>-33.55995188</v>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="46">
         <v>120.02013530000001</v>
       </c>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F24" s="48" t="s">
+      <c r="F24" s="47" t="s">
         <v>370</v>
       </c>
-      <c r="G24" s="48" t="s">
+      <c r="G24" s="47" t="s">
         <v>371</v>
       </c>
-      <c r="H24" s="47" t="s">
+      <c r="H24" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="I24" s="51" t="s">
+      <c r="I24" s="50" t="s">
         <v>359</v>
       </c>
-      <c r="J24" s="50">
+      <c r="J24" s="49">
         <v>800</v>
       </c>
-      <c r="K24" s="50" t="s">
+      <c r="K24" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50">
+      <c r="L24" s="49"/>
+      <c r="M24" s="49">
         <v>9.4</v>
       </c>
-      <c r="N24" s="50" t="s">
+      <c r="N24" s="49" t="s">
         <v>372</v>
       </c>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="33" t="s">
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="S24" s="33" t="s">
+      <c r="S24" s="32" t="s">
         <v>374</v>
       </c>
-      <c r="W24" s="33"/>
-      <c r="X24" s="33"/>
-      <c r="Y24" s="33"/>
-    </row>
-    <row r="25" spans="1:25">
-      <c r="A25" s="46" t="s">
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A25" s="45" t="s">
         <v>375</v>
       </c>
-      <c r="B25" s="48">
+      <c r="B25" s="47">
         <v>-31.080956489999998</v>
       </c>
-      <c r="C25" s="47">
+      <c r="C25" s="46">
         <v>121.43617829999999</v>
       </c>
-      <c r="D25" s="48" t="s">
+      <c r="D25" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E25" s="48" t="s">
+      <c r="E25" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F25" s="48" t="s">
+      <c r="F25" s="47" t="s">
         <v>376</v>
       </c>
-      <c r="G25" s="48" t="s">
+      <c r="G25" s="47" t="s">
         <v>377</v>
       </c>
-      <c r="H25" s="47" t="s">
+      <c r="H25" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="I25" s="51" t="s">
+      <c r="I25" s="50" t="s">
         <v>359</v>
       </c>
-      <c r="J25" s="50">
+      <c r="J25" s="49">
         <v>600</v>
       </c>
-      <c r="K25" s="50"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50">
+      <c r="K25" s="49"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="49">
         <v>66.099999999999994</v>
       </c>
-      <c r="N25" s="50" t="s">
+      <c r="N25" s="49" t="s">
         <v>378</v>
       </c>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33" t="s">
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="S25" s="33" t="s">
+      <c r="S25" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="X25" s="33"/>
-      <c r="Y25" s="33"/>
-    </row>
-    <row r="26" spans="1:25">
-      <c r="A26" s="46" t="s">
+      <c r="X25" s="32"/>
+      <c r="Y25" s="32"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A26" s="45" t="s">
         <v>381</v>
       </c>
-      <c r="B26" s="48">
+      <c r="B26" s="47">
         <v>-21.048112459999999</v>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="46">
         <v>118.8972516</v>
       </c>
-      <c r="D26" s="48" t="s">
+      <c r="D26" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E26" s="48" t="s">
+      <c r="E26" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F26" s="48" t="s">
+      <c r="F26" s="47" t="s">
         <v>382</v>
       </c>
-      <c r="G26" s="48" t="s">
+      <c r="G26" s="47" t="s">
         <v>383</v>
       </c>
-      <c r="H26" s="47" t="s">
+      <c r="H26" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="51" t="s">
+      <c r="I26" s="50" t="s">
         <v>359</v>
       </c>
-      <c r="J26" s="50">
+      <c r="J26" s="49">
         <v>680</v>
       </c>
-      <c r="K26" s="50" t="s">
+      <c r="K26" s="49" t="s">
         <v>384</v>
       </c>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50">
+      <c r="L26" s="49"/>
+      <c r="M26" s="49">
         <v>413.8</v>
       </c>
-      <c r="N26" s="50" t="s">
+      <c r="N26" s="49" t="s">
         <v>385</v>
       </c>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33" t="s">
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32" t="s">
         <v>386</v>
       </c>
-      <c r="W26" s="33"/>
-      <c r="X26" s="33"/>
-      <c r="Y26" s="33"/>
-    </row>
-    <row r="27" spans="1:25">
-      <c r="A27" s="46" t="s">
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A27" s="45" t="s">
         <v>387</v>
       </c>
-      <c r="B27" s="48">
+      <c r="B27" s="47">
         <v>-21.177731099999999</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="46">
         <v>118.6745341</v>
       </c>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E27" s="48" t="s">
+      <c r="E27" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F27" s="48" t="s">
+      <c r="F27" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="G27" s="48">
+      <c r="G27" s="47">
         <v>2019</v>
       </c>
-      <c r="H27" s="47"/>
-      <c r="I27" s="51" t="s">
+      <c r="H27" s="46"/>
+      <c r="I27" s="50" t="s">
         <v>359</v>
       </c>
-      <c r="J27" s="50">
+      <c r="J27" s="49">
         <v>900</v>
       </c>
-      <c r="K27" s="50"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50">
+      <c r="K27" s="49"/>
+      <c r="L27" s="49"/>
+      <c r="M27" s="49">
         <v>217.4</v>
       </c>
-      <c r="N27" s="50" t="s">
+      <c r="N27" s="49" t="s">
         <v>385</v>
       </c>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="33" t="s">
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32" t="s">
         <v>389</v>
       </c>
-      <c r="Y27" s="33"/>
-    </row>
-    <row r="28" spans="1:25">
-      <c r="A28" s="46" t="s">
+      <c r="Y27" s="32"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A28" s="45" t="s">
         <v>390</v>
       </c>
-      <c r="B28" s="48">
+      <c r="B28" s="47">
         <v>-32.103731689999996</v>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="46">
         <v>119.7682851</v>
       </c>
-      <c r="D28" s="48" t="s">
+      <c r="D28" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E28" s="48" t="s">
+      <c r="E28" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F28" s="48" t="s">
+      <c r="F28" s="47" t="s">
         <v>391</v>
       </c>
-      <c r="G28" s="48" t="s">
+      <c r="G28" s="47" t="s">
         <v>392</v>
       </c>
-      <c r="H28" s="47" t="s">
+      <c r="H28" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="51" t="s">
+      <c r="I28" s="50" t="s">
         <v>393</v>
       </c>
-      <c r="J28" s="50">
+      <c r="J28" s="49">
         <v>380</v>
       </c>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33" t="s">
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32" t="s">
         <v>394</v>
       </c>
-      <c r="W28" s="33"/>
-      <c r="X28" s="33"/>
-      <c r="Y28" s="33"/>
-    </row>
-    <row r="29" spans="1:25">
-      <c r="A29" s="46" t="s">
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A29" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="B29" s="47">
+      <c r="B29" s="46">
         <v>-24.4117</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="46">
         <v>119.7058</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E29" s="48" t="s">
+      <c r="E29" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F29" s="48" t="s">
+      <c r="F29" s="47" t="s">
         <v>396</v>
       </c>
-      <c r="G29" s="48" t="s">
+      <c r="G29" s="47" t="s">
         <v>397</v>
       </c>
-      <c r="H29" s="48" t="s">
+      <c r="H29" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I29" s="49" t="s">
+      <c r="I29" s="48" t="s">
         <v>398</v>
       </c>
-      <c r="J29" s="50">
+      <c r="J29" s="49">
         <v>312</v>
       </c>
-      <c r="K29" s="50"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="50">
+      <c r="K29" s="49"/>
+      <c r="L29" s="49"/>
+      <c r="M29" s="49">
         <v>274</v>
       </c>
-      <c r="N29" s="50" t="s">
+      <c r="N29" s="49" t="s">
         <v>399</v>
       </c>
-      <c r="O29" s="33"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="33" t="s">
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="W29" s="33"/>
-      <c r="X29" s="33"/>
-      <c r="Y29" s="33"/>
-    </row>
-    <row r="30" spans="1:25">
-      <c r="A30" s="46" t="s">
+      <c r="W29" s="32"/>
+      <c r="X29" s="32"/>
+      <c r="Y29" s="32"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A30" s="45" t="s">
         <v>401</v>
       </c>
-      <c r="B30" s="47">
+      <c r="B30" s="46">
         <v>-13.9922</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="46">
         <v>136.44550000000001</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="D30" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="E30" s="48" t="s">
+      <c r="E30" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F30" s="48" t="s">
+      <c r="F30" s="47" t="s">
         <v>402</v>
       </c>
-      <c r="G30" s="48" t="s">
+      <c r="G30" s="47" t="s">
         <v>403</v>
       </c>
-      <c r="H30" s="48"/>
-      <c r="I30" s="49" t="s">
+      <c r="H30" s="47"/>
+      <c r="I30" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="J30" s="50" t="s">
+      <c r="J30" s="49" t="s">
         <v>405</v>
       </c>
-      <c r="K30" s="50" t="s">
+      <c r="K30" s="49" t="s">
         <v>406</v>
       </c>
-      <c r="L30" s="50"/>
-      <c r="M30" s="50">
+      <c r="L30" s="49"/>
+      <c r="M30" s="49">
         <v>138</v>
       </c>
-      <c r="N30" s="50" t="s">
+      <c r="N30" s="49" t="s">
         <v>407</v>
       </c>
-      <c r="O30" s="33"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="33"/>
-      <c r="R30" s="33" t="s">
+      <c r="O30" s="32"/>
+      <c r="P30" s="32"/>
+      <c r="Q30" s="32"/>
+      <c r="R30" s="32" t="s">
         <v>408</v>
       </c>
-      <c r="S30" s="33" t="s">
+      <c r="S30" s="32" t="s">
         <v>409</v>
       </c>
-      <c r="X30" s="33"/>
-      <c r="Y30" s="33"/>
-    </row>
-    <row r="31" spans="1:25">
-      <c r="A31" s="46" t="s">
+      <c r="X30" s="32"/>
+      <c r="Y30" s="32"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" s="45" t="s">
         <v>410</v>
       </c>
-      <c r="B31" s="47">
+      <c r="B31" s="46">
         <v>-21.6388</v>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="46">
         <v>121.2355</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E31" s="48" t="s">
+      <c r="E31" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F31" s="48" t="s">
+      <c r="F31" s="47" t="s">
         <v>411</v>
       </c>
-      <c r="G31" s="48" t="s">
+      <c r="G31" s="47" t="s">
         <v>412</v>
       </c>
-      <c r="H31" s="48" t="s">
+      <c r="H31" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="49" t="s">
+      <c r="I31" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="J31" s="50">
+      <c r="J31" s="49">
         <v>1500</v>
       </c>
-      <c r="K31" s="50" t="s">
+      <c r="K31" s="49" t="s">
         <v>398</v>
       </c>
-      <c r="L31" s="50"/>
-      <c r="M31" s="50">
+      <c r="L31" s="49"/>
+      <c r="M31" s="49">
         <v>36.5</v>
       </c>
-      <c r="N31" s="53" t="s">
+      <c r="N31" s="52" t="s">
         <v>413</v>
       </c>
-      <c r="O31" s="33"/>
-      <c r="P31" s="33"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="33" t="s">
+      <c r="O31" s="32"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32" t="s">
         <v>414</v>
       </c>
-      <c r="W31" s="33"/>
-      <c r="X31" s="33"/>
-      <c r="Y31" s="33"/>
-    </row>
-    <row r="32" spans="1:25">
-      <c r="A32" s="46" t="s">
+      <c r="W31" s="32"/>
+      <c r="X31" s="32"/>
+      <c r="Y31" s="32"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="B32" s="47">
+      <c r="B32" s="46">
         <v>-41.920299999999997</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="46">
         <v>145.24850000000001</v>
       </c>
-      <c r="D32" s="48" t="s">
+      <c r="D32" s="47" t="s">
         <v>416</v>
       </c>
-      <c r="E32" s="48" t="s">
+      <c r="E32" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F32" s="48" t="s">
+      <c r="F32" s="47" t="s">
         <v>417</v>
       </c>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="51" t="s">
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50" t="s">
+      <c r="J32" s="49"/>
+      <c r="K32" s="49" t="s">
         <v>419</v>
       </c>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="33"/>
-      <c r="X32" s="33"/>
-      <c r="Y32" s="33"/>
-    </row>
-    <row r="33" spans="1:25">
-      <c r="A33" s="46" t="s">
+      <c r="L32" s="49"/>
+      <c r="M32" s="49"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A33" s="45" t="s">
         <v>420</v>
       </c>
-      <c r="B33" s="54">
+      <c r="B33" s="53">
         <v>-27.59</v>
       </c>
-      <c r="C33" s="54">
+      <c r="C33" s="53">
         <v>120.57599999999999</v>
       </c>
-      <c r="D33" s="48" t="s">
+      <c r="D33" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E33" s="48" t="s">
+      <c r="E33" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F33" s="48" t="s">
+      <c r="F33" s="47" t="s">
         <v>421</v>
       </c>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="51" t="s">
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
-      <c r="L33" s="50"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="33"/>
-      <c r="Y33" s="33"/>
-    </row>
-    <row r="34" spans="1:25">
-      <c r="A34" s="46" t="s">
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="49"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="32"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A34" s="45" t="s">
         <v>422</v>
       </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48" t="s">
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="47" t="s">
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="I34" s="51" t="s">
+      <c r="I34" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J34" s="50"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="50"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="X34" s="33"/>
-      <c r="Y34" s="33"/>
-    </row>
-    <row r="35" spans="1:25">
-      <c r="A35" s="46" t="s">
+      <c r="J34" s="49"/>
+      <c r="K34" s="49"/>
+      <c r="L34" s="49"/>
+      <c r="M34" s="49"/>
+      <c r="N34" s="49"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="32"/>
+      <c r="Q34" s="32"/>
+      <c r="X34" s="32"/>
+      <c r="Y34" s="32"/>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A35" s="45" t="s">
         <v>423</v>
       </c>
-      <c r="B35" s="48">
+      <c r="B35" s="47">
         <v>-32.474345710000001</v>
       </c>
-      <c r="C35" s="48">
+      <c r="C35" s="47">
         <v>119.6736746</v>
       </c>
-      <c r="D35" s="48" t="s">
+      <c r="D35" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E35" s="48" t="s">
+      <c r="E35" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F35" s="48" t="s">
+      <c r="F35" s="47" t="s">
         <v>421</v>
       </c>
-      <c r="G35" s="48" t="s">
+      <c r="G35" s="47" t="s">
         <v>424</v>
       </c>
-      <c r="H35" s="48"/>
-      <c r="I35" s="51" t="s">
+      <c r="H35" s="47"/>
+      <c r="I35" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J35" s="50">
+      <c r="J35" s="49">
         <v>22.9</v>
       </c>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="33"/>
-      <c r="P35" s="33"/>
-      <c r="Q35" s="33"/>
-      <c r="V35" s="33"/>
-      <c r="W35" s="33"/>
-      <c r="X35" s="33"/>
-      <c r="Y35" s="33"/>
-    </row>
-    <row r="36" spans="1:25">
-      <c r="A36" s="46" t="s">
+      <c r="K35" s="49"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="32"/>
+      <c r="X35" s="32"/>
+      <c r="Y35" s="32"/>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A36" s="45" t="s">
         <v>425</v>
       </c>
-      <c r="B36" s="54">
+      <c r="B36" s="53">
         <v>-31.189240999999999</v>
       </c>
-      <c r="C36" s="54">
+      <c r="C36" s="53">
         <v>121.66873099999999</v>
       </c>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48" t="s">
+      <c r="D36" s="47"/>
+      <c r="E36" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F36" s="48" t="s">
+      <c r="F36" s="47" t="s">
         <v>426</v>
       </c>
-      <c r="G36" s="48" t="s">
+      <c r="G36" s="47" t="s">
         <v>427</v>
       </c>
-      <c r="H36" s="48"/>
-      <c r="I36" s="51" t="s">
+      <c r="H36" s="47"/>
+      <c r="I36" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J36" s="50">
+      <c r="J36" s="49">
         <v>1.4</v>
       </c>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33"/>
-      <c r="V36" s="33"/>
-      <c r="W36" s="33"/>
-      <c r="X36" s="33"/>
-      <c r="Y36" s="33"/>
-    </row>
-    <row r="37" spans="1:25">
-      <c r="A37" s="46" t="s">
+      <c r="K36" s="49"/>
+      <c r="L36" s="49"/>
+      <c r="M36" s="49"/>
+      <c r="N36" s="49"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="32"/>
+      <c r="X36" s="32"/>
+      <c r="Y36" s="32"/>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A37" s="45" t="s">
         <v>428</v>
       </c>
-      <c r="B37" s="54">
+      <c r="B37" s="53">
         <v>-27.233587</v>
       </c>
-      <c r="C37" s="54">
+      <c r="C37" s="53">
         <v>120.59360700000001</v>
       </c>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48" t="s">
+      <c r="D37" s="47"/>
+      <c r="E37" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F37" s="48" t="s">
+      <c r="F37" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="51" t="s">
+      <c r="G37" s="47"/>
+      <c r="H37" s="47"/>
+      <c r="I37" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="33"/>
-      <c r="V37" s="33"/>
-      <c r="W37" s="33"/>
-      <c r="X37" s="33"/>
-      <c r="Y37" s="33"/>
-    </row>
-    <row r="38" spans="1:25">
-      <c r="A38" s="46" t="s">
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="49"/>
+      <c r="N37" s="49"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="V37" s="32"/>
+      <c r="W37" s="32"/>
+      <c r="X37" s="32"/>
+      <c r="Y37" s="32"/>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A38" s="45" t="s">
         <v>429</v>
       </c>
-      <c r="B38" s="48">
+      <c r="B38" s="47">
         <v>-27.232889790000002</v>
       </c>
-      <c r="C38" s="48">
+      <c r="C38" s="47">
         <v>120.55561640000001</v>
       </c>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E38" s="48" t="s">
+      <c r="E38" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F38" s="48" t="s">
+      <c r="F38" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="G38" s="48" t="s">
+      <c r="G38" s="47" t="s">
         <v>430</v>
       </c>
-      <c r="H38" s="48"/>
-      <c r="I38" s="51" t="s">
+      <c r="H38" s="47"/>
+      <c r="I38" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J38" s="50">
+      <c r="J38" s="49">
         <v>80</v>
       </c>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33"/>
+      <c r="K38" s="49"/>
+      <c r="L38" s="49"/>
+      <c r="M38" s="49"/>
+      <c r="N38" s="49"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
       <c r="R38" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="X38" s="33"/>
-      <c r="Y38" s="33"/>
-    </row>
-    <row r="39" spans="1:25">
-      <c r="A39" s="46" t="s">
+      <c r="X38" s="32"/>
+      <c r="Y38" s="32"/>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A39" s="45" t="s">
         <v>432</v>
       </c>
-      <c r="B39" s="48">
+      <c r="B39" s="47">
         <v>-28.76693393</v>
       </c>
-      <c r="C39" s="48">
+      <c r="C39" s="47">
         <v>121.8958611</v>
       </c>
-      <c r="D39" s="48" t="s">
+      <c r="D39" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E39" s="48" t="s">
+      <c r="E39" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F39" s="48" t="s">
+      <c r="F39" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="G39" s="48">
+      <c r="G39" s="47">
         <v>1999</v>
       </c>
-      <c r="H39" s="48"/>
-      <c r="I39" s="51" t="s">
+      <c r="H39" s="47"/>
+      <c r="I39" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J39" s="50">
+      <c r="J39" s="49">
         <v>35.700000000000003</v>
       </c>
-      <c r="K39" s="50" t="s">
+      <c r="K39" s="49" t="s">
         <v>419</v>
       </c>
-      <c r="L39" s="50">
+      <c r="L39" s="49">
         <v>3.3</v>
       </c>
-      <c r="M39" s="50">
+      <c r="M39" s="49">
         <v>205</v>
       </c>
-      <c r="N39" s="50" t="s">
+      <c r="N39" s="49" t="s">
         <v>433</v>
       </c>
-      <c r="O39" s="33"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="33" t="s">
+      <c r="O39" s="32"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32" t="s">
         <v>434</v>
       </c>
-      <c r="W39" s="33"/>
-      <c r="X39" s="33"/>
-      <c r="Y39" s="33"/>
-    </row>
-    <row r="40" spans="1:25">
-      <c r="A40" s="46" t="s">
+      <c r="W39" s="32"/>
+      <c r="X39" s="32"/>
+      <c r="Y39" s="32"/>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A40" s="45" t="s">
         <v>336</v>
       </c>
-      <c r="B40" s="48">
+      <c r="B40" s="47">
         <v>-31.809779509999998</v>
       </c>
-      <c r="C40" s="48">
+      <c r="C40" s="47">
         <v>123.17348819999999</v>
       </c>
-      <c r="D40" s="48" t="s">
+      <c r="D40" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E40" s="48" t="s">
+      <c r="E40" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F40" s="48" t="s">
+      <c r="F40" s="47" t="s">
         <v>435</v>
       </c>
-      <c r="G40" s="48">
+      <c r="G40" s="47">
         <v>2017</v>
       </c>
-      <c r="H40" s="48"/>
-      <c r="I40" s="51" t="s">
+      <c r="H40" s="47"/>
+      <c r="I40" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J40" s="50">
+      <c r="J40" s="49">
         <v>23</v>
       </c>
-      <c r="K40" s="50" t="s">
+      <c r="K40" s="49" t="s">
         <v>436</v>
       </c>
-      <c r="L40" s="50">
+      <c r="L40" s="49">
         <v>0.80300000000000005</v>
       </c>
-      <c r="M40" s="50">
+      <c r="M40" s="49">
         <v>14.3</v>
       </c>
-      <c r="N40" s="50" t="s">
+      <c r="N40" s="49" t="s">
         <v>437</v>
       </c>
-      <c r="O40" s="33"/>
-      <c r="P40" s="33"/>
-      <c r="Q40" s="33"/>
-      <c r="R40" s="33" t="s">
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32" t="s">
         <v>438</v>
       </c>
-      <c r="W40" s="33"/>
-      <c r="X40" s="33"/>
-      <c r="Y40" s="33"/>
-    </row>
-    <row r="41" spans="1:25">
-      <c r="A41" s="46" t="s">
+      <c r="W40" s="32"/>
+      <c r="X40" s="32"/>
+      <c r="Y40" s="32"/>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A41" s="45" t="s">
         <v>439</v>
       </c>
-      <c r="B41" s="48">
+      <c r="B41" s="47">
         <v>-33.6432012</v>
       </c>
-      <c r="C41" s="48">
+      <c r="C41" s="47">
         <v>120.38330000000001</v>
       </c>
-      <c r="D41" s="48" t="s">
+      <c r="D41" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E41" s="48" t="s">
+      <c r="E41" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F41" s="48" t="s">
+      <c r="F41" s="47" t="s">
         <v>440</v>
       </c>
-      <c r="G41" s="48" t="s">
+      <c r="G41" s="47" t="s">
         <v>441</v>
       </c>
-      <c r="H41" s="48"/>
-      <c r="I41" s="51" t="s">
+      <c r="H41" s="47"/>
+      <c r="I41" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J41" s="50">
+      <c r="J41" s="49">
         <v>16.8</v>
       </c>
-      <c r="K41" s="50" t="s">
+      <c r="K41" s="49" t="s">
         <v>419</v>
       </c>
-      <c r="L41" s="50">
+      <c r="L41" s="49">
         <v>0.84</v>
       </c>
-      <c r="M41" s="50">
+      <c r="M41" s="49">
         <v>211.6</v>
       </c>
-      <c r="N41" s="50" t="s">
+      <c r="N41" s="49" t="s">
         <v>442</v>
       </c>
-      <c r="O41" s="33"/>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="33" t="s">
+      <c r="O41" s="32"/>
+      <c r="P41" s="32"/>
+      <c r="Q41" s="32"/>
+      <c r="R41" s="32" t="s">
         <v>443</v>
       </c>
-      <c r="S41" s="33" t="s">
+      <c r="S41" s="32" t="s">
         <v>444</v>
       </c>
-      <c r="X41" s="33"/>
-      <c r="Y41" s="33"/>
-    </row>
-    <row r="42" spans="1:25">
-      <c r="A42" s="46" t="s">
+      <c r="X41" s="32"/>
+      <c r="Y41" s="32"/>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A42" s="45" t="s">
         <v>445</v>
       </c>
-      <c r="B42" s="54">
+      <c r="B42" s="53">
         <v>-17.361574999999998</v>
       </c>
-      <c r="C42" s="54">
+      <c r="C42" s="53">
         <v>128.03310500000001</v>
       </c>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48" t="s">
+      <c r="D42" s="47"/>
+      <c r="E42" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48" t="s">
+      <c r="F42" s="47"/>
+      <c r="G42" s="47" t="s">
         <v>446</v>
       </c>
-      <c r="H42" s="48"/>
-      <c r="I42" s="51" t="s">
+      <c r="H42" s="47"/>
+      <c r="I42" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="J42" s="50"/>
-      <c r="K42" s="50" t="s">
+      <c r="J42" s="49"/>
+      <c r="K42" s="49" t="s">
         <v>447</v>
       </c>
-      <c r="L42" s="50"/>
-      <c r="M42" s="50"/>
-      <c r="N42" s="50"/>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="33"/>
-      <c r="X42" s="33"/>
-      <c r="Y42" s="33"/>
-    </row>
-    <row r="43" spans="1:25">
-      <c r="A43" s="46" t="s">
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="49"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="X42" s="32"/>
+      <c r="Y42" s="32"/>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A43" s="45" t="s">
         <v>448</v>
       </c>
-      <c r="B43" s="48">
+      <c r="B43" s="47">
         <v>-18.859500000000001</v>
       </c>
-      <c r="C43" s="47">
+      <c r="C43" s="46">
         <v>128.93979999999999</v>
       </c>
-      <c r="D43" s="48" t="s">
+      <c r="D43" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E43" s="48" t="s">
+      <c r="E43" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F43" s="48" t="s">
+      <c r="F43" s="47" t="s">
         <v>449</v>
       </c>
-      <c r="G43" s="48" t="s">
+      <c r="G43" s="47" t="s">
         <v>450</v>
       </c>
-      <c r="H43" s="48" t="s">
+      <c r="H43" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I43" s="49" t="s">
+      <c r="I43" s="48" t="s">
         <v>451</v>
       </c>
-      <c r="J43" s="50" t="s">
+      <c r="J43" s="49" t="s">
         <v>452</v>
       </c>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
-      <c r="M43" s="50">
+      <c r="K43" s="49"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="49">
         <v>7.3</v>
       </c>
-      <c r="N43" s="50" t="s">
+      <c r="N43" s="49" t="s">
         <v>453</v>
       </c>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="33" t="s">
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="32" t="s">
         <v>454</v>
       </c>
-      <c r="W43" s="33"/>
-      <c r="X43" s="33"/>
-      <c r="Y43" s="33"/>
-    </row>
-    <row r="44" spans="1:25">
-      <c r="A44" s="46" t="s">
+      <c r="W43" s="32"/>
+      <c r="X43" s="32"/>
+      <c r="Y43" s="32"/>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A44" s="45" t="s">
         <v>455</v>
       </c>
-      <c r="B44" s="48">
+      <c r="B44" s="47">
         <v>-23.895600000000002</v>
       </c>
-      <c r="C44" s="48">
+      <c r="C44" s="47">
         <v>116.1893</v>
       </c>
-      <c r="D44" s="48" t="s">
+      <c r="D44" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E44" s="48" t="s">
+      <c r="E44" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F44" s="48" t="s">
+      <c r="F44" s="47" t="s">
         <v>456</v>
       </c>
-      <c r="G44" s="48" t="s">
+      <c r="G44" s="47" t="s">
         <v>457</v>
       </c>
-      <c r="H44" s="48" t="s">
+      <c r="H44" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="49" t="s">
+      <c r="I44" s="48" t="s">
         <v>458</v>
       </c>
-      <c r="J44" s="50">
+      <c r="J44" s="49">
         <v>37</v>
       </c>
-      <c r="K44" s="50" t="s">
+      <c r="K44" s="49" t="s">
         <v>459</v>
       </c>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50">
+      <c r="L44" s="49"/>
+      <c r="M44" s="49">
         <v>29.93</v>
       </c>
-      <c r="N44" s="50" t="s">
+      <c r="N44" s="49" t="s">
         <v>460</v>
       </c>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="33" t="s">
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
+      <c r="R44" s="32" t="s">
         <v>461</v>
       </c>
-      <c r="S44" s="33"/>
-      <c r="T44" s="40" t="s">
+      <c r="S44" s="32"/>
+      <c r="T44" s="39" t="s">
         <v>462</v>
       </c>
-      <c r="W44" s="33"/>
-      <c r="X44" s="33"/>
-      <c r="Y44" s="33"/>
-    </row>
-    <row r="45" spans="1:25">
-      <c r="A45" s="46" t="s">
+      <c r="W44" s="32"/>
+      <c r="X44" s="32"/>
+      <c r="Y44" s="32"/>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A45" s="45" t="s">
         <v>463</v>
       </c>
-      <c r="B45" s="48">
+      <c r="B45" s="47">
         <v>-28.861750539999999</v>
       </c>
-      <c r="C45" s="48">
+      <c r="C45" s="47">
         <v>122.548373</v>
       </c>
-      <c r="D45" s="48" t="s">
+      <c r="D45" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="E45" s="48" t="s">
+      <c r="E45" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="48" t="s">
+      <c r="F45" s="47" t="s">
         <v>464</v>
       </c>
-      <c r="G45" s="48" t="s">
+      <c r="G45" s="47" t="s">
         <v>465</v>
       </c>
-      <c r="H45" s="48" t="s">
+      <c r="H45" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I45" s="49" t="s">
+      <c r="I45" s="48" t="s">
         <v>466</v>
       </c>
-      <c r="J45" s="50">
+      <c r="J45" s="49">
         <v>12</v>
       </c>
-      <c r="K45" s="50" t="s">
+      <c r="K45" s="49" t="s">
         <v>467</v>
       </c>
-      <c r="L45" s="50"/>
-      <c r="M45" s="50">
+      <c r="L45" s="49"/>
+      <c r="M45" s="49">
         <v>106.6</v>
       </c>
-      <c r="N45" s="50" t="s">
+      <c r="N45" s="49" t="s">
         <v>468</v>
       </c>
-      <c r="O45" s="33"/>
-      <c r="P45" s="33"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="33" t="s">
+      <c r="O45" s="32"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32" t="s">
         <v>469</v>
       </c>
-      <c r="S45" s="33" t="s">
+      <c r="S45" s="32" t="s">
         <v>470</v>
       </c>
-      <c r="T45" s="40" t="s">
+      <c r="T45" s="39" t="s">
         <v>471</v>
       </c>
-      <c r="W45" s="33"/>
-      <c r="X45" s="33"/>
-      <c r="Y45" s="33"/>
-    </row>
-    <row r="46" spans="1:25">
-      <c r="A46" s="46" t="s">
+      <c r="W45" s="32"/>
+      <c r="X45" s="32"/>
+      <c r="Y45" s="32"/>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" s="45" t="s">
         <v>472</v>
       </c>
-      <c r="B46" s="48">
+      <c r="B46" s="47">
         <v>-16.43389616</v>
       </c>
-      <c r="C46" s="48">
+      <c r="C46" s="47">
         <v>136.09125320000001</v>
       </c>
-      <c r="D46" s="48" t="s">
+      <c r="D46" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="E46" s="48" t="s">
+      <c r="E46" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F46" s="48" t="s">
+      <c r="F46" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="G46" s="48" t="s">
+      <c r="G46" s="47" t="s">
         <v>473</v>
       </c>
-      <c r="H46" s="48" t="s">
+      <c r="H46" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I46" s="51" t="s">
+      <c r="I46" s="50" t="s">
         <v>474</v>
       </c>
-      <c r="J46" s="50">
+      <c r="J46" s="49">
         <v>271</v>
       </c>
-      <c r="K46" s="50" t="s">
+      <c r="K46" s="49" t="s">
         <v>475</v>
       </c>
-      <c r="L46" s="50"/>
-      <c r="M46" s="50">
+      <c r="L46" s="49"/>
+      <c r="M46" s="49">
         <v>127</v>
       </c>
-      <c r="N46" s="50" t="s">
+      <c r="N46" s="49" t="s">
         <v>476</v>
       </c>
-      <c r="O46" s="33"/>
-      <c r="P46" s="33"/>
-      <c r="Q46" s="33"/>
-      <c r="R46" s="33" t="s">
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32" t="s">
         <v>477</v>
       </c>
-      <c r="W46" s="33"/>
-      <c r="X46" s="33"/>
-      <c r="Y46" s="33"/>
-    </row>
-    <row r="47" spans="1:25">
-      <c r="A47" s="46" t="s">
+      <c r="W46" s="32"/>
+      <c r="X46" s="32"/>
+      <c r="Y46" s="32"/>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" s="45" t="s">
         <v>478</v>
       </c>
-      <c r="B47" s="48">
+      <c r="B47" s="47">
         <v>-21.855800389999999</v>
       </c>
-      <c r="C47" s="48">
+      <c r="C47" s="47">
         <v>140.90720189999999</v>
       </c>
-      <c r="D47" s="48" t="s">
+      <c r="D47" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="E47" s="48" t="s">
+      <c r="E47" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F47" s="48" t="s">
+      <c r="F47" s="47" t="s">
         <v>479</v>
       </c>
-      <c r="G47" s="48" t="s">
+      <c r="G47" s="47" t="s">
         <v>480</v>
       </c>
-      <c r="H47" s="48" t="s">
+      <c r="H47" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I47" s="51" t="s">
+      <c r="I47" s="50" t="s">
         <v>481</v>
       </c>
-      <c r="J47" s="50">
+      <c r="J47" s="49">
         <v>59.2</v>
       </c>
-      <c r="K47" s="50" t="s">
+      <c r="K47" s="49" t="s">
         <v>475</v>
       </c>
-      <c r="L47" s="50"/>
-      <c r="M47" s="50">
+      <c r="L47" s="49"/>
+      <c r="M47" s="49">
         <v>80</v>
       </c>
-      <c r="N47" s="50" t="s">
+      <c r="N47" s="49" t="s">
         <v>482</v>
       </c>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="33" t="s">
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32" t="s">
         <v>483</v>
       </c>
-      <c r="W47" s="33"/>
-      <c r="X47" s="33"/>
-      <c r="Y47" s="33"/>
-    </row>
-    <row r="48" spans="1:25">
-      <c r="A48" s="46" t="s">
+      <c r="W47" s="32"/>
+      <c r="X47" s="32"/>
+      <c r="Y47" s="32"/>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" s="45" t="s">
         <v>484</v>
       </c>
-      <c r="B48" s="48">
+      <c r="B48" s="47">
         <v>-18.733029219999999</v>
       </c>
-      <c r="C48" s="48">
+      <c r="C48" s="47">
         <v>138.61928449999999</v>
       </c>
-      <c r="D48" s="48" t="s">
+      <c r="D48" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="E48" s="48" t="s">
+      <c r="E48" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F48" s="48" t="s">
+      <c r="F48" s="47" t="s">
         <v>485</v>
       </c>
-      <c r="G48" s="48" t="s">
+      <c r="G48" s="47" t="s">
         <v>486</v>
       </c>
-      <c r="H48" s="48" t="s">
+      <c r="H48" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I48" s="51" t="s">
+      <c r="I48" s="50" t="s">
         <v>481</v>
       </c>
-      <c r="J48" s="50">
+      <c r="J48" s="49">
         <v>116</v>
       </c>
-      <c r="K48" s="50" t="s">
+      <c r="K48" s="49" t="s">
         <v>487</v>
       </c>
-      <c r="L48" s="50"/>
-      <c r="M48" s="50">
+      <c r="L48" s="49"/>
+      <c r="M48" s="49">
         <v>10.5</v>
       </c>
-      <c r="N48" s="50" t="s">
+      <c r="N48" s="49" t="s">
         <v>488</v>
       </c>
-      <c r="O48" s="33"/>
-      <c r="P48" s="33"/>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33" t="s">
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32" t="s">
         <v>489</v>
       </c>
-      <c r="W48" s="33"/>
-      <c r="X48" s="33"/>
-      <c r="Y48" s="33"/>
-    </row>
-    <row r="49" spans="1:25">
-      <c r="A49" s="46" t="s">
+      <c r="W48" s="32"/>
+      <c r="X48" s="32"/>
+      <c r="Y48" s="32"/>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A49" s="45" t="s">
         <v>490</v>
       </c>
-      <c r="B49" s="48">
+      <c r="B49" s="47">
         <v>-20.234643479999999</v>
       </c>
-      <c r="C49" s="48">
+      <c r="C49" s="47">
         <v>140.18932469999999</v>
       </c>
-      <c r="D49" s="48" t="s">
+      <c r="D49" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="E49" s="48" t="s">
+      <c r="E49" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F49" s="48" t="s">
+      <c r="F49" s="47" t="s">
         <v>491</v>
       </c>
-      <c r="G49" s="48" t="s">
+      <c r="G49" s="47" t="s">
         <v>492</v>
       </c>
-      <c r="H49" s="48" t="s">
+      <c r="H49" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I49" s="51" t="s">
+      <c r="I49" s="50" t="s">
         <v>481</v>
       </c>
-      <c r="J49" s="50">
+      <c r="J49" s="49">
         <v>151.84</v>
       </c>
-      <c r="K49" s="50" t="s">
+      <c r="K49" s="49" t="s">
         <v>493</v>
       </c>
-      <c r="L49" s="50"/>
-      <c r="M49" s="50">
+      <c r="L49" s="49"/>
+      <c r="M49" s="49">
         <v>66</v>
       </c>
-      <c r="N49" s="50" t="s">
+      <c r="N49" s="49" t="s">
         <v>494</v>
       </c>
-      <c r="O49" s="33"/>
-      <c r="P49" s="33"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="33" t="s">
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32" t="s">
         <v>495</v>
       </c>
-      <c r="W49" s="33"/>
-      <c r="X49" s="33"/>
-      <c r="Y49" s="33"/>
-    </row>
-    <row r="50" spans="1:25">
-      <c r="A50" s="46" t="s">
+      <c r="W49" s="32"/>
+      <c r="X49" s="32"/>
+      <c r="Y49" s="32"/>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A50" s="45" t="s">
         <v>496</v>
       </c>
-      <c r="B50" s="48">
+      <c r="B50" s="47">
         <v>-31.16243549</v>
       </c>
-      <c r="C50" s="48">
+      <c r="C50" s="47">
         <v>145.6552634</v>
       </c>
-      <c r="D50" s="48" t="s">
+      <c r="D50" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="E50" s="48" t="s">
+      <c r="E50" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F50" s="48" t="s">
+      <c r="F50" s="47" t="s">
         <v>497</v>
       </c>
-      <c r="G50" s="48" t="s">
+      <c r="G50" s="47" t="s">
         <v>498</v>
       </c>
-      <c r="H50" s="48" t="s">
+      <c r="H50" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I50" s="51" t="s">
+      <c r="I50" s="50" t="s">
         <v>481</v>
       </c>
-      <c r="J50" s="50">
+      <c r="J50" s="49">
         <v>10</v>
       </c>
-      <c r="K50" s="50" t="s">
+      <c r="K50" s="49" t="s">
         <v>499</v>
       </c>
-      <c r="L50" s="50"/>
-      <c r="M50" s="50">
+      <c r="L50" s="49"/>
+      <c r="M50" s="49">
         <v>21.5</v>
       </c>
-      <c r="N50" s="50" t="s">
+      <c r="N50" s="49" t="s">
         <v>500</v>
       </c>
-      <c r="O50" s="33"/>
-      <c r="P50" s="33"/>
-      <c r="Q50" s="33"/>
-      <c r="R50" s="33" t="s">
+      <c r="O50" s="32"/>
+      <c r="P50" s="32"/>
+      <c r="Q50" s="32"/>
+      <c r="R50" s="32" t="s">
         <v>501</v>
       </c>
-      <c r="W50" s="33"/>
-      <c r="X50" s="33"/>
-      <c r="Y50" s="33"/>
-    </row>
-    <row r="51" spans="1:25">
-      <c r="A51" s="33"/>
-      <c r="B51" s="33"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="33"/>
-      <c r="M51" s="33"/>
-      <c r="N51" s="33"/>
-      <c r="O51" s="33"/>
-      <c r="P51" s="33"/>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="33"/>
-      <c r="S51" s="33"/>
-      <c r="T51" s="33"/>
-      <c r="U51" s="33"/>
-      <c r="V51" s="33"/>
+      <c r="W50" s="32"/>
+      <c r="X50" s="32"/>
+      <c r="Y50" s="32"/>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A51" s="32"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="N51" s="32"/>
+      <c r="O51" s="32"/>
+      <c r="P51" s="32"/>
+      <c r="Q51" s="32"/>
+      <c r="R51" s="32"/>
+      <c r="S51" s="32"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
+      <c r="V51" s="32"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y50">
